--- a/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
+++ b/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
@@ -7360,7 +7360,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7597,7 +7597,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7718,7 +7718,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7839,7 +7839,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7960,7 +7960,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8081,7 +8081,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
+++ b/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
@@ -5936,7 +5936,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5955,7 +5955,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
+++ b/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
@@ -6249,7 +6249,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6268,7 +6268,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6775,7 +6775,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6794,7 +6794,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7037,7 +7037,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -7056,7 +7056,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36578,7 +36578,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>33</v>
@@ -39147,7 +39147,7 @@
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">PL!D67</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">PL!E67</f>
@@ -39186,7 +39186,7 @@
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">PL!G71</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>367</v>
@@ -39205,11 +39205,11 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">PL!E72/fx</f>
-        <v>152.518489568968</v>
+        <v>152.518489568969</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">PL!F72/fx</f>
-        <v>183.668243317853</v>
+        <v>183.668243317854</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">PL!G72/fx</f>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">PL!E74/fx</f>
-        <v>137.266640612071</v>
+        <v>137.266640612072</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">PL!F74/fx</f>
@@ -39287,7 +39287,7 @@
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">PL!F81</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">PL!G81</f>
@@ -39306,7 +39306,7 @@
       </c>
       <c r="C12" s="16" t="n">
         <f aca="false">PL!D80</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">PL!E80</f>
@@ -39360,7 +39360,7 @@
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">PL!D67-PL!D72/fx</f>
-        <v>549.643837535011</v>
+        <v>549.64383753501</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">PL!E67-PL!E72/fx</f>
@@ -39464,7 +39464,7 @@
       </c>
       <c r="F5" s="19" t="n">
         <f aca="false">F77</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G5" s="19" t="n">
         <f aca="false">G77</f>
@@ -39484,11 +39484,11 @@
       </c>
       <c r="E6" s="15" t="n">
         <f aca="false">E78</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">F78</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G6" s="15" t="n">
         <f aca="false">G78</f>
@@ -39516,11 +39516,11 @@
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">F74</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">G74</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39572,11 +39572,11 @@
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">F79</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">G79</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39596,7 +39596,7 @@
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">E85</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">F85</f>
@@ -39708,15 +39708,15 @@
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">E95</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">F95</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">G95</f>
-        <v>56.0341822636685</v>
+        <v>56.0341822636686</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39732,7 +39732,7 @@
       </c>
       <c r="E15" s="15" t="n">
         <f aca="false">E96</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F15" s="15" t="n">
         <f aca="false">F96</f>
@@ -39740,7 +39740,7 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G96</f>
-        <v>0.0791465814032595</v>
+        <v>0.0791465814032593</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39789,7 +39789,7 @@
       </c>
       <c r="E19" s="15" t="n">
         <f aca="false">E117</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">F117</f>
@@ -39877,7 +39877,7 @@
       </c>
       <c r="F22" s="15" t="n">
         <f aca="false">F118</f>
-        <v>0.736707319102774</v>
+        <v>0.736707319102775</v>
       </c>
       <c r="G22" s="15" t="n">
         <f aca="false">G118</f>
@@ -39901,7 +39901,7 @@
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E124</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">F124</f>
@@ -39993,7 +39993,7 @@
       </c>
       <c r="G26" s="19" t="n">
         <f aca="false">G132</f>
-        <v>184.059363955116</v>
+        <v>184.059363955117</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40013,15 +40013,15 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">E134</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">F134</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">G134</f>
-        <v>47.7505532893189</v>
+        <v>47.750553289319</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40037,15 +40037,15 @@
       </c>
       <c r="E28" s="15" t="n">
         <f aca="false">E135</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F28" s="15" t="n">
         <f aca="false">F135</f>
-        <v>-0.0377764581389647</v>
+        <v>-0.0377764581389645</v>
       </c>
       <c r="G28" s="15" t="n">
         <f aca="false">G135</f>
-        <v>0.137878955138602</v>
+        <v>0.137878955138601</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="E32" s="15" t="n">
         <f aca="false">E156</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F32" s="15" t="n">
         <f aca="false">F156</f>
@@ -40102,7 +40102,7 @@
       </c>
       <c r="G32" s="15" t="n">
         <f aca="false">G156</f>
-        <v>0.01441407281165</v>
+        <v>0.0144140728116497</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40182,7 +40182,7 @@
       </c>
       <c r="F35" s="15" t="n">
         <f aca="false">F157</f>
-        <v>0.677267463701926</v>
+        <v>0.677267463701927</v>
       </c>
       <c r="G35" s="15" t="n">
         <f aca="false">G157</f>
@@ -40206,7 +40206,7 @@
       </c>
       <c r="E36" s="19" t="n">
         <f aca="false">E163</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F36" s="19" t="n">
         <f aca="false">F163</f>
@@ -40318,11 +40318,11 @@
       </c>
       <c r="E40" s="16" t="n">
         <f aca="false">E173</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F40" s="16" t="n">
         <f aca="false">F173</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
       <c r="G40" s="16" t="n">
         <f aca="false">G173</f>
@@ -40342,7 +40342,7 @@
       </c>
       <c r="E41" s="15" t="n">
         <f aca="false">E174</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F41" s="15" t="n">
         <f aca="false">F174</f>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="G41" s="15" t="n">
         <f aca="false">G174</f>
-        <v>0.0815142604669075</v>
+        <v>0.081514260466907</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40430,7 +40430,7 @@
       </c>
       <c r="D63" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -40529,7 +40529,7 @@
       </c>
       <c r="D67" s="19" t="n">
         <f aca="false">D65*D66</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E67" s="19" t="n">
         <f aca="false">E65*E66</f>
@@ -40553,7 +40553,7 @@
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">D67*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E68" s="19" t="n">
         <f aca="false">E67*fx</f>
@@ -40628,7 +40628,7 @@
       </c>
       <c r="G71" s="15" t="n">
         <f aca="false">$D$69*G70</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="G72" s="19" t="n">
         <f aca="false">G68*G71</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40703,11 +40703,11 @@
       </c>
       <c r="F74" s="19" t="n">
         <f aca="false">F72*(1-F73)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G74" s="19" t="n">
         <f aca="false">G72*(1-G73)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="F77" s="19" t="n">
         <f aca="false">F74+F76</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G77" s="19" t="n">
         <f aca="false">G74+G76</f>
@@ -40784,11 +40784,11 @@
       </c>
       <c r="E78" s="15" t="n">
         <f aca="false">E77/D77-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F78" s="15" t="n">
         <f aca="false">F77/E77-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G78" s="15" t="n">
         <f aca="false">G77/F77-1</f>
@@ -40816,11 +40816,11 @@
       </c>
       <c r="F79" s="15" t="n">
         <f aca="false">F74/F77</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G79" s="15" t="n">
         <f aca="false">G74/G77</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40832,7 +40832,7 @@
       </c>
       <c r="D80" s="16" t="n">
         <f aca="false">D74/fx/D65</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E80" s="16" t="n">
         <f aca="false">E74/fx/E65</f>
@@ -40864,7 +40864,7 @@
       </c>
       <c r="F81" s="19" t="n">
         <f aca="false">F72/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G81" s="19" t="n">
         <f aca="false">G72/fx/odm_vr</f>
@@ -40907,7 +40907,7 @@
       </c>
       <c r="E84" s="21" t="n">
         <f aca="false">($D$83+d_ai+vrd)*E72*(1-E73*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F84" s="21" t="n">
         <f aca="false">($D$83+d_ai+vrd)*F72*(1-F73*(1-keep))</f>
@@ -40915,7 +40915,7 @@
       </c>
       <c r="G84" s="21" t="n">
         <f aca="false">($D$83+d_ai+vrd)*G72*(1-G73*(1-keep))</f>
-        <v>248.799436346374</v>
+        <v>248.799436346375</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>423</v>
@@ -40938,7 +40938,7 @@
       </c>
       <c r="E85" s="19" t="n">
         <f aca="false">$D$83*E76+E84</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F85" s="19" t="n">
         <f aca="false">$D$83*F76+F84</f>
@@ -41021,7 +41021,7 @@
       </c>
       <c r="E88" s="19" t="n">
         <f aca="false">D88*(1+MAX(0,phi*E78))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F88" s="19" t="n">
         <f aca="false">E88*(1+MAX(0,phi*F78))</f>
@@ -41029,7 +41029,7 @@
       </c>
       <c r="G88" s="19" t="n">
         <f aca="false">F88*(1+MAX(0,phi*G78))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41049,7 +41049,7 @@
       </c>
       <c r="E89" s="19" t="n">
         <f aca="false">E88+0*E77</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F89" s="19" t="n">
         <f aca="false">F88+0*F77</f>
@@ -41057,7 +41057,7 @@
       </c>
       <c r="G89" s="19" t="n">
         <f aca="false">G88+0*G77</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41085,7 +41085,7 @@
       </c>
       <c r="G90" s="19" t="n">
         <f aca="false">G85-G89</f>
-        <v>249.698791091313</v>
+        <v>249.698791091314</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41217,15 +41217,15 @@
       </c>
       <c r="E95" s="21" t="n">
         <f aca="false">E93/E94</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F95" s="21" t="n">
         <f aca="false">F93/F94</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="G95" s="21" t="n">
         <f aca="false">G93/G94</f>
-        <v>56.0341822636685</v>
+        <v>56.0341822636686</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="E96" s="15" t="n">
         <f aca="false">E95/D95-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F96" s="15" t="n">
         <f aca="false">F95/E95-1</f>
@@ -41249,7 +41249,7 @@
       </c>
       <c r="G96" s="15" t="n">
         <f aca="false">G95/F95-1</f>
-        <v>0.0791465814032595</v>
+        <v>0.0791465814032593</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="D102" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E102" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="D106" s="19" t="n">
         <f aca="false">D104*D105</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E106" s="19" t="n">
         <f aca="false">E104*E105</f>
@@ -41420,7 +41420,7 @@
       </c>
       <c r="D107" s="19" t="n">
         <f aca="false">D106*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E107" s="19" t="n">
         <f aca="false">E106*fx</f>
@@ -41495,7 +41495,7 @@
       </c>
       <c r="G110" s="15" t="n">
         <f aca="false">$D$108*G109</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41515,11 +41515,11 @@
       </c>
       <c r="F111" s="19" t="n">
         <f aca="false">F107*F110</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G111" s="19" t="n">
         <f aca="false">G107*G110</f>
-        <v>5391.45372814681</v>
+        <v>5391.45372814682</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41651,7 +41651,7 @@
       </c>
       <c r="E117" s="15" t="n">
         <f aca="false">E116/D116-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F117" s="15" t="n">
         <f aca="false">F116/E116-1</f>
@@ -41683,7 +41683,7 @@
       </c>
       <c r="F118" s="15" t="n">
         <f aca="false">F113/F116</f>
-        <v>0.736707319102774</v>
+        <v>0.736707319102775</v>
       </c>
       <c r="G118" s="15" t="n">
         <f aca="false">G113/G116</f>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="D119" s="16" t="n">
         <f aca="false">D113/fx/D104</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E119" s="16" t="n">
         <f aca="false">E113/fx/E104</f>
@@ -41774,7 +41774,7 @@
       </c>
       <c r="E123" s="21" t="n">
         <f aca="false">($D$122+d_ai+vrd)*E111*(1-E112*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F123" s="21" t="n">
         <f aca="false">($D$122+d_ai+vrd)*F111*(1-F112*(1-keep))</f>
@@ -41782,7 +41782,7 @@
       </c>
       <c r="G123" s="21" t="n">
         <f aca="false">($D$122+d_ai+vrd)*G111*(1-G112*(1-keep))</f>
-        <v>211.479520894418</v>
+        <v>211.479520894419</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>423</v>
@@ -41805,7 +41805,7 @@
       </c>
       <c r="E124" s="19" t="n">
         <f aca="false">$D$122*E115+E123</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F124" s="19" t="n">
         <f aca="false">$D$122*F115+F123</f>
@@ -41888,11 +41888,11 @@
       </c>
       <c r="E127" s="19" t="n">
         <f aca="false">D127*(1+MAX(0,phi*E117))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F127" s="19" t="n">
         <f aca="false">E127*(1+MAX(0,phi*F117))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G127" s="19" t="n">
         <f aca="false">F127*(1+MAX(0,phi*G117))</f>
@@ -41916,11 +41916,11 @@
       </c>
       <c r="E128" s="19" t="n">
         <f aca="false">E127+0*E116</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F128" s="19" t="n">
         <f aca="false">F127+0*F116</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G128" s="19" t="n">
         <f aca="false">G127+0*G116</f>
@@ -42036,7 +42036,7 @@
       </c>
       <c r="G132" s="19" t="n">
         <f aca="false">G129*G131</f>
-        <v>184.059363955116</v>
+        <v>184.059363955117</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42084,15 +42084,15 @@
       </c>
       <c r="E134" s="21" t="n">
         <f aca="false">E132/E133</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F134" s="21" t="n">
         <f aca="false">F132/F133</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="G134" s="21" t="n">
         <f aca="false">G132/G133</f>
-        <v>47.7505532893189</v>
+        <v>47.750553289319</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42108,15 +42108,15 @@
       </c>
       <c r="E135" s="15" t="n">
         <f aca="false">E134/D134-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F135" s="15" t="n">
         <f aca="false">F134/E134-1</f>
-        <v>-0.0377764581389647</v>
+        <v>-0.0377764581389645</v>
       </c>
       <c r="G135" s="15" t="n">
         <f aca="false">G134/F134-1</f>
-        <v>0.137878955138602</v>
+        <v>0.137878955138601</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42164,7 +42164,7 @@
       </c>
       <c r="D141" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E141" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -42263,7 +42263,7 @@
       </c>
       <c r="D145" s="19" t="n">
         <f aca="false">D143*D144</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E145" s="19" t="n">
         <f aca="false">E143*E144</f>
@@ -42287,7 +42287,7 @@
       </c>
       <c r="D146" s="19" t="n">
         <f aca="false">D145*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E146" s="19" t="n">
         <f aca="false">E145*fx</f>
@@ -42362,7 +42362,7 @@
       </c>
       <c r="G149" s="15" t="n">
         <f aca="false">$D$147*G148</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="F150" s="19" t="n">
         <f aca="false">F146*F149</f>
-        <v>3526.43027170278</v>
+        <v>3526.43027170279</v>
       </c>
       <c r="G150" s="19" t="n">
         <f aca="false">G146*G149</f>
@@ -42518,7 +42518,7 @@
       </c>
       <c r="E156" s="15" t="n">
         <f aca="false">E155/D155-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F156" s="15" t="n">
         <f aca="false">F155/E155-1</f>
@@ -42526,7 +42526,7 @@
       </c>
       <c r="G156" s="15" t="n">
         <f aca="false">G155/F155-1</f>
-        <v>0.01441407281165</v>
+        <v>0.0144140728116497</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42550,7 +42550,7 @@
       </c>
       <c r="F157" s="15" t="n">
         <f aca="false">F152/F155</f>
-        <v>0.677267463701926</v>
+        <v>0.677267463701927</v>
       </c>
       <c r="G157" s="15" t="n">
         <f aca="false">G152/G155</f>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="D158" s="16" t="n">
         <f aca="false">D152/fx/D143</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E158" s="16" t="n">
         <f aca="false">E152/fx/E143</f>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="G159" s="19" t="n">
         <f aca="false">G150/fx/odm_vr</f>
-        <v>17.6191298305451</v>
+        <v>17.6191298305452</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>418</v>
@@ -42641,7 +42641,7 @@
       </c>
       <c r="E162" s="21" t="n">
         <f aca="false">($D$161+d_ai+vrd)*E150*(1-E151*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F162" s="21" t="n">
         <f aca="false">($D$161+d_ai+vrd)*F150*(1-F151*(1-keep))</f>
@@ -42672,7 +42672,7 @@
       </c>
       <c r="E163" s="19" t="n">
         <f aca="false">$D$161*E154+E162</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F163" s="19" t="n">
         <f aca="false">$D$161*F154+F162</f>
@@ -42755,15 +42755,15 @@
       </c>
       <c r="E166" s="19" t="n">
         <f aca="false">D166*(1+MAX(0,phi*E156))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F166" s="19" t="n">
         <f aca="false">E166*(1+MAX(0,phi*F156))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G166" s="19" t="n">
         <f aca="false">F166*(1+MAX(0,phi*G156))</f>
-        <v>83.8601773129817</v>
+        <v>83.8601773129818</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42783,15 +42783,15 @@
       </c>
       <c r="E167" s="19" t="n">
         <f aca="false">E166+0*E155</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F167" s="19" t="n">
         <f aca="false">F166+0*F155</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G167" s="19" t="n">
         <f aca="false">G166+0*G155</f>
-        <v>83.8601773129817</v>
+        <v>83.8601773129818</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42951,11 +42951,11 @@
       </c>
       <c r="E173" s="21" t="n">
         <f aca="false">E171/E172</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F173" s="21" t="n">
         <f aca="false">F171/F172</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
       <c r="G173" s="21" t="n">
         <f aca="false">G171/G172</f>
@@ -42975,7 +42975,7 @@
       </c>
       <c r="E174" s="15" t="n">
         <f aca="false">E173/D173-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F174" s="15" t="n">
         <f aca="false">F173/E173-1</f>
@@ -42983,7 +42983,7 @@
       </c>
       <c r="G174" s="15" t="n">
         <f aca="false">G173/F173-1</f>
-        <v>0.0815142604669075</v>
+        <v>0.081514260466907</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="F180" s="19" t="n">
         <f aca="false">F77</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G180" s="19" t="n">
         <f aca="false">G77</f>
@@ -43060,11 +43060,11 @@
       </c>
       <c r="H180" s="23" t="n">
         <f aca="false">G180*(1+H181)</f>
-        <v>6306.46270294503</v>
+        <v>6306.46270294504</v>
       </c>
       <c r="I180" s="23" t="n">
         <f aca="false">H180*(1+I181)</f>
-        <v>6587.28124797557</v>
+        <v>6587.28124797558</v>
       </c>
       <c r="J180" s="23" t="n">
         <f aca="false">I180*(1+J181)</f>
@@ -43088,11 +43088,11 @@
       </c>
       <c r="E181" s="15" t="n">
         <f aca="false">E180/D180-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F181" s="15" t="n">
         <f aca="false">F180/E180-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G181" s="15" t="n">
         <f aca="false">G180/F180-1</f>
@@ -43172,7 +43172,7 @@
       </c>
       <c r="F183" s="15" t="n">
         <f aca="false">F182/F180</f>
-        <v>0.0331029355689947</v>
+        <v>0.0331029355689948</v>
       </c>
       <c r="G183" s="15" t="n">
         <f aca="false">G182/G180</f>
@@ -43251,15 +43251,15 @@
       </c>
       <c r="E185" s="16" t="n">
         <f aca="false">E95</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F185" s="16" t="n">
         <f aca="false">F95</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="G185" s="16" t="n">
         <f aca="false">G95</f>
-        <v>56.0341822636685</v>
+        <v>56.0341822636686</v>
       </c>
       <c r="H185" s="26" t="n">
         <f aca="false">H182/H184</f>
@@ -43288,7 +43288,7 @@
       </c>
       <c r="E186" s="15" t="n">
         <f aca="false">E185/D185-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F186" s="15" t="n">
         <f aca="false">F185/E185-1</f>
@@ -43296,7 +43296,7 @@
       </c>
       <c r="G186" s="15" t="n">
         <f aca="false">G185/F185-1</f>
-        <v>0.0791465814032595</v>
+        <v>0.0791465814032593</v>
       </c>
       <c r="H186" s="24" t="n">
         <f aca="false">H185/G185-1</f>
@@ -43304,7 +43304,7 @@
       </c>
       <c r="I186" s="24" t="n">
         <f aca="false">I185/H185-1</f>
-        <v>0.0445286935415319</v>
+        <v>0.0445286935415317</v>
       </c>
       <c r="J186" s="24" t="n">
         <f aca="false">J185/I185-1</f>
@@ -43410,11 +43410,11 @@
       </c>
       <c r="H192" s="23" t="n">
         <f aca="false">G192*(1+H193)</f>
-        <v>5705.44103724899</v>
+        <v>5705.441037249</v>
       </c>
       <c r="I192" s="23" t="n">
         <f aca="false">H192*(1+I193)</f>
-        <v>5972.66327803759</v>
+        <v>5972.6632780376</v>
       </c>
       <c r="J192" s="23" t="n">
         <f aca="false">I192*(1+J193)</f>
@@ -43438,7 +43438,7 @@
       </c>
       <c r="E193" s="15" t="n">
         <f aca="false">E192/D192-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F193" s="15" t="n">
         <f aca="false">F192/E192-1</f>
@@ -43486,7 +43486,7 @@
       </c>
       <c r="G194" s="19" t="n">
         <f aca="false">G132</f>
-        <v>184.059363955116</v>
+        <v>184.059363955117</v>
       </c>
       <c r="H194" s="23" t="n">
         <f aca="false">H192*H195</f>
@@ -43522,7 +43522,7 @@
       </c>
       <c r="F195" s="15" t="n">
         <f aca="false">F194/F192</f>
-        <v>0.0316805572174471</v>
+        <v>0.0316805572174472</v>
       </c>
       <c r="G195" s="15" t="n">
         <f aca="false">G194/G192</f>
@@ -43601,15 +43601,15 @@
       </c>
       <c r="E197" s="16" t="n">
         <f aca="false">E134</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F197" s="16" t="n">
         <f aca="false">F134</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="G197" s="16" t="n">
         <f aca="false">G134</f>
-        <v>47.7505532893189</v>
+        <v>47.750553289319</v>
       </c>
       <c r="H197" s="26" t="n">
         <f aca="false">H194/H196</f>
@@ -43617,7 +43617,7 @@
       </c>
       <c r="I197" s="26" t="n">
         <f aca="false">I194/I196</f>
-        <v>49.158627873752</v>
+        <v>49.1586278737521</v>
       </c>
       <c r="J197" s="26" t="n">
         <f aca="false">J194/J196</f>
@@ -43638,19 +43638,19 @@
       </c>
       <c r="E198" s="15" t="n">
         <f aca="false">E197/D197-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F198" s="15" t="n">
         <f aca="false">F197/E197-1</f>
-        <v>-0.0377764581389647</v>
+        <v>-0.0377764581389645</v>
       </c>
       <c r="G198" s="15" t="n">
         <f aca="false">G197/F197-1</f>
-        <v>0.137878955138602</v>
+        <v>0.137878955138601</v>
       </c>
       <c r="H198" s="24" t="n">
         <f aca="false">H197/G197-1</f>
-        <v>0.0185503469673451</v>
+        <v>0.0185503469673449</v>
       </c>
       <c r="I198" s="24" t="n">
         <f aca="false">I197/H197-1</f>
@@ -43658,7 +43658,7 @@
       </c>
       <c r="J198" s="24" t="n">
         <f aca="false">J197/I197-1</f>
-        <v>0.00285714285714267</v>
+        <v>0.00285714285714289</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43764,11 +43764,11 @@
       </c>
       <c r="I204" s="23" t="n">
         <f aca="false">H204*(1+I205)</f>
-        <v>4372.18659765542</v>
+        <v>4372.18659765543</v>
       </c>
       <c r="J204" s="23" t="n">
         <f aca="false">I204*(1+J205)</f>
-        <v>4459.63032960853</v>
+        <v>4459.63032960854</v>
       </c>
       <c r="K204" s="8" t="s">
         <v>437</v>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="E205" s="15" t="n">
         <f aca="false">E204/D204-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F205" s="15" t="n">
         <f aca="false">F204/E204-1</f>
@@ -43796,15 +43796,15 @@
       </c>
       <c r="G205" s="15" t="n">
         <f aca="false">G204/F204-1</f>
-        <v>0.01441407281165</v>
+        <v>0.0144140728116497</v>
       </c>
       <c r="H205" s="24" t="n">
         <f aca="false">$G$205+($C$211-$G$205)*1/3</f>
-        <v>0.0162760485411</v>
+        <v>0.0162760485410998</v>
       </c>
       <c r="I205" s="24" t="n">
         <f aca="false">$G$205+($C$211-$G$205)*2/3</f>
-        <v>0.01813802427055</v>
+        <v>0.0181380242705499</v>
       </c>
       <c r="J205" s="24" t="n">
         <f aca="false">$G$205+($C$211-$G$205)*3/3</f>
@@ -43951,11 +43951,11 @@
       </c>
       <c r="E209" s="16" t="n">
         <f aca="false">E173</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F209" s="16" t="n">
         <f aca="false">F173</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
       <c r="G209" s="16" t="n">
         <f aca="false">G173</f>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="I209" s="26" t="n">
         <f aca="false">I206/I208</f>
-        <v>30.6126971472798</v>
+        <v>30.6126971472799</v>
       </c>
       <c r="J209" s="26" t="n">
         <f aca="false">J206/J208</f>
@@ -43988,7 +43988,7 @@
       </c>
       <c r="E210" s="15" t="n">
         <f aca="false">E209/D209-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F210" s="15" t="n">
         <f aca="false">F209/E209-1</f>
@@ -43996,19 +43996,19 @@
       </c>
       <c r="G210" s="15" t="n">
         <f aca="false">G209/F209-1</f>
-        <v>0.0815142604669075</v>
+        <v>0.081514260466907</v>
       </c>
       <c r="H210" s="24" t="n">
         <f aca="false">H209/G209-1</f>
-        <v>-0.0514756880283067</v>
+        <v>-0.0514756880283066</v>
       </c>
       <c r="I210" s="24" t="n">
         <f aca="false">I209/H209-1</f>
-        <v>-0.0545861203202036</v>
+        <v>-0.0545861203202037</v>
       </c>
       <c r="J210" s="24" t="n">
         <f aca="false">J209/I209-1</f>
-        <v>-0.0584615384615383</v>
+        <v>-0.0584615384615382</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44098,7 +44098,7 @@
       </c>
       <c r="F217" s="19" t="n">
         <f aca="false">F182+F180*da_r-F180*cx_r</f>
-        <v>192.529694638339</v>
+        <v>192.52969463834</v>
       </c>
       <c r="G217" s="19" t="n">
         <f aca="false">G182+G180*da_r-G180*cx_r</f>
@@ -44106,7 +44106,7 @@
       </c>
       <c r="H217" s="23" t="n">
         <f aca="false">H182+H180*da_r-H180*cx_r</f>
-        <v>214.318949507256</v>
+        <v>214.318949507257</v>
       </c>
       <c r="I217" s="23" t="n">
         <f aca="false">I182+I180*da_r-I180*cx_r</f>
@@ -44141,7 +44141,7 @@
       </c>
       <c r="G218" s="19" t="n">
         <f aca="false">G194+G192*da_r-G192*cx_r</f>
-        <v>177.236312362925</v>
+        <v>177.236312362926</v>
       </c>
       <c r="H218" s="23" t="n">
         <f aca="false">H194+H192*da_r-H192*cx_r</f>
@@ -44311,11 +44311,11 @@
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">px/PL!F14</f>
-        <v>6.20130758001893</v>
+        <v>6.20130758001892</v>
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">px/PL!F27</f>
-        <v>7.67314718501047</v>
+        <v>7.67314718501046</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">px/PL!F40</f>
@@ -44328,15 +44328,15 @@
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">px/PL!G14</f>
-        <v>5.74649235505626</v>
+        <v>5.74649235505625</v>
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">px/PL!G27</f>
-        <v>6.74337736044677</v>
+        <v>6.74337736044676</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">px/PL!G40</f>
-        <v>9.43245446916549</v>
+        <v>9.43245446916548</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44345,7 +44345,7 @@
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">0.2*PL!D14+0.8*PL!E14</f>
-        <v>40.6341224968788</v>
+        <v>40.6341224968789</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44500,11 +44500,11 @@
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">PL!E14</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">B23</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D23" s="29" t="n">
         <f aca="false">D17</f>
@@ -44516,7 +44516,7 @@
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">E23/px-1</f>
-        <v>0.661862376131592</v>
+        <v>0.661862376131595</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">px/C23</f>
@@ -44529,11 +44529,11 @@
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">PL!E27</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C24" s="28" t="n">
         <f aca="false">B24</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D24" s="29" t="n">
         <f aca="false">D18</f>
@@ -44541,11 +44541,11 @@
       </c>
       <c r="E24" s="30" t="n">
         <f aca="false">C24*D24</f>
-        <v>471.446112150478</v>
+        <v>471.446112150479</v>
       </c>
       <c r="F24" s="31" t="n">
         <f aca="false">E24/px-1</f>
-        <v>0.464118360715771</v>
+        <v>0.464118360715773</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">px/C24</f>
@@ -44558,11 +44558,11 @@
       </c>
       <c r="B25" s="28" t="n">
         <f aca="false">PL!E40</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C25" s="28" t="n">
         <f aca="false">B25</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D25" s="29" t="n">
         <f aca="false">D19</f>
@@ -44570,11 +44570,11 @@
       </c>
       <c r="E25" s="30" t="n">
         <f aca="false">C25*D25</f>
-        <v>471.446112150478</v>
+        <v>471.446112150479</v>
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">E25/px-1</f>
-        <v>0.464118360715771</v>
+        <v>0.464118360715773</v>
       </c>
       <c r="G25" s="29" t="n">
         <f aca="false">px/C25</f>
@@ -44609,7 +44609,7 @@
       </c>
       <c r="B28" s="18" t="n">
         <f aca="false">px*A28/PL!F14</f>
-        <v>6.20130758001893</v>
+        <v>6.20130758001892</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">px*A28/PL!F40</f>
@@ -44630,7 +44630,7 @@
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">px*A29/PL!F14</f>
-        <v>6.82143833802082</v>
+        <v>6.82143833802081</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">px*A29/PL!F40</f>
@@ -44651,7 +44651,7 @@
       </c>
       <c r="B30" s="18" t="n">
         <f aca="false">px*A30/PL!F14</f>
-        <v>7.5035821718229</v>
+        <v>7.50358217182289</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">px*A30/PL!F40</f>
@@ -44672,7 +44672,7 @@
       </c>
       <c r="B31" s="18" t="n">
         <f aca="false">px*A31/PL!F14</f>
-        <v>9.30196137002839</v>
+        <v>9.30196137002838</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">px*A31/PL!F40</f>
@@ -44693,7 +44693,7 @@
       </c>
       <c r="B32" s="18" t="n">
         <f aca="false">px*A32/PL!F14</f>
-        <v>12.4026151600379</v>
+        <v>12.4026151600378</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">px*A32/PL!F40</f>
@@ -44747,11 +44747,11 @@
       </c>
       <c r="B37" s="16" t="n">
         <f aca="false">PL!E14</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C37" s="27" t="n">
         <f aca="false">B37*pe_fair_andy</f>
-        <v>654.1805441496</v>
+        <v>654.180544149601</v>
       </c>
       <c r="D37" s="32" t="n">
         <f aca="false">C37/px-1</f>
@@ -44759,11 +44759,11 @@
       </c>
       <c r="E37" s="16" t="n">
         <f aca="false">PL!F14</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="F37" s="27" t="n">
         <f aca="false">E37*pe_fair_andy</f>
-        <v>778.867994802035</v>
+        <v>778.867994802036</v>
       </c>
       <c r="G37" s="32" t="n">
         <f aca="false">F37/px-1</f>
@@ -44776,11 +44776,11 @@
       </c>
       <c r="B38" s="16" t="n">
         <f aca="false">PL!E27</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C38" s="27" t="n">
         <f aca="false">B38*pe_fair_andy</f>
-        <v>654.1805441496</v>
+        <v>654.180544149601</v>
       </c>
       <c r="D38" s="32" t="n">
         <f aca="false">C38/px-1</f>
@@ -44788,7 +44788,7 @@
       </c>
       <c r="E38" s="16" t="n">
         <f aca="false">PL!F27</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="F38" s="27" t="n">
         <f aca="false">E38*pe_fair_andy</f>
@@ -44796,7 +44796,7 @@
       </c>
       <c r="G38" s="32" t="n">
         <f aca="false">F38/px-1</f>
-        <v>0.954869317416794</v>
+        <v>0.954869317416796</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44805,11 +44805,11 @@
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">PL!E40</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C39" s="27" t="n">
         <f aca="false">B39*pe_fair_andy</f>
-        <v>654.1805441496</v>
+        <v>654.180544149601</v>
       </c>
       <c r="D39" s="32" t="n">
         <f aca="false">C39/px-1</f>
@@ -44817,7 +44817,7 @@
       </c>
       <c r="E39" s="16" t="n">
         <f aca="false">PL!F40</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
       <c r="F39" s="27" t="n">
         <f aca="false">E39*pe_fair_andy</f>
@@ -44825,7 +44825,7 @@
       </c>
       <c r="G39" s="32" t="n">
         <f aca="false">F39/px-1</f>
-        <v>0.470395927745285</v>
+        <v>0.470395927745287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44853,7 +44853,7 @@
       </c>
       <c r="B43" s="35" t="n">
         <f aca="false">B42/px-1</f>
-        <v>0.523441565340518</v>
+        <v>0.523441565340519</v>
       </c>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -44879,7 +44879,7 @@
       </c>
       <c r="B45" s="27" t="n">
         <f aca="false">E24</f>
-        <v>471.446112150478</v>
+        <v>471.446112150479</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>507</v>
@@ -44891,7 +44891,7 @@
       </c>
       <c r="B46" s="27" t="n">
         <f aca="false">E25</f>
-        <v>471.446112150478</v>
+        <v>471.446112150479</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>509</v>
@@ -45234,15 +45234,15 @@
       </c>
       <c r="E78" s="21" t="n">
         <f aca="false">C23</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F78" s="19" t="n">
         <f aca="false">C78*E78</f>
-        <v>471.446112150478</v>
+        <v>471.446112150479</v>
       </c>
       <c r="G78" s="15" t="n">
         <f aca="false">F78/px-1</f>
-        <v>0.464118360715771</v>
+        <v>0.464118360715773</v>
       </c>
       <c r="H78" s="16" t="n">
         <f aca="false">px/E78</f>
@@ -45265,7 +45265,7 @@
       </c>
       <c r="E79" s="21" t="n">
         <f aca="false">C23</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F79" s="19" t="n">
         <f aca="false">C79*E79</f>
@@ -45273,7 +45273,7 @@
       </c>
       <c r="G79" s="15" t="n">
         <f aca="false">F79/px-1</f>
-        <v>0.661862376131592</v>
+        <v>0.661862376131595</v>
       </c>
       <c r="H79" s="16" t="n">
         <f aca="false">px/E79</f>
@@ -45296,15 +45296,15 @@
       </c>
       <c r="E80" s="21" t="n">
         <f aca="false">C23</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F80" s="19" t="n">
         <f aca="false">C80*E80</f>
-        <v>637.17185000171</v>
+        <v>637.171850001711</v>
       </c>
       <c r="G80" s="15" t="n">
         <f aca="false">F80/px-1</f>
-        <v>0.978794565222703</v>
+        <v>0.978794565222705</v>
       </c>
       <c r="H80" s="16" t="n">
         <f aca="false">px/E80</f>
@@ -45352,15 +45352,15 @@
       </c>
       <c r="B89" s="16" t="n">
         <f aca="false">PL!E185</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="C89" s="16" t="n">
         <f aca="false">PL!E197</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D89" s="16" t="n">
         <f aca="false">PL!E209</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45369,15 +45369,15 @@
       </c>
       <c r="B90" s="16" t="n">
         <f aca="false">PL!F185</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="C90" s="16" t="n">
         <f aca="false">PL!F197</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="D90" s="16" t="n">
         <f aca="false">PL!F209</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45386,11 +45386,11 @@
       </c>
       <c r="B91" s="16" t="n">
         <f aca="false">PL!G185</f>
-        <v>56.0341822636685</v>
+        <v>56.0341822636686</v>
       </c>
       <c r="C91" s="16" t="n">
         <f aca="false">PL!G197</f>
-        <v>47.7505532893189</v>
+        <v>47.750553289319</v>
       </c>
       <c r="D91" s="16" t="n">
         <f aca="false">PL!G209</f>
@@ -45424,11 +45424,11 @@
       </c>
       <c r="C93" s="16" t="n">
         <f aca="false">PL!I197</f>
-        <v>49.158627873752</v>
+        <v>49.1586278737521</v>
       </c>
       <c r="D93" s="16" t="n">
         <f aca="false">PL!I209</f>
-        <v>30.6126971472798</v>
+        <v>30.6126971472799</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45471,15 +45471,15 @@
       </c>
       <c r="B97" s="16" t="n">
         <f aca="false">B89*(1-$B$96)</f>
-        <v>37.1882675848555</v>
+        <v>37.1882675848556</v>
       </c>
       <c r="C97" s="16" t="n">
         <f aca="false">C89*(1-$B$96)</f>
-        <v>37.1882675848555</v>
+        <v>37.1882675848556</v>
       </c>
       <c r="D97" s="16" t="n">
         <f aca="false">D89*(1-$B$96)</f>
-        <v>37.1882675848555</v>
+        <v>37.1882675848556</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45488,15 +45488,15 @@
       </c>
       <c r="B98" s="16" t="n">
         <f aca="false">B90*(1-$B$96)</f>
-        <v>44.2763877082749</v>
+        <v>44.276387708275</v>
       </c>
       <c r="C98" s="16" t="n">
         <f aca="false">C90*(1-$B$96)</f>
-        <v>35.7834265511756</v>
+        <v>35.7834265511757</v>
       </c>
       <c r="D98" s="16" t="n">
         <f aca="false">D90*(1-$B$96)</f>
-        <v>26.9152542386561</v>
+        <v>26.9152542386562</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="B100" s="16" t="n">
         <f aca="false">B92*(1-$B$96)</f>
-        <v>49.1690950885192</v>
+        <v>49.1690950885193</v>
       </c>
       <c r="C100" s="16" t="n">
         <f aca="false">C92*(1-$B$96)</f>
@@ -45539,7 +45539,7 @@
       </c>
       <c r="B101" s="16" t="n">
         <f aca="false">B93*(1-$B$96)</f>
-        <v>51.3585306554303</v>
+        <v>51.3585306554304</v>
       </c>
       <c r="C101" s="16" t="n">
         <f aca="false">C93*(1-$B$96)</f>
@@ -45547,7 +45547,7 @@
       </c>
       <c r="D101" s="16" t="n">
         <f aca="false">D93*(1-$B$96)</f>
-        <v>26.1036463829818</v>
+        <v>26.1036463829819</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45556,7 +45556,7 @@
       </c>
       <c r="B102" s="16" t="n">
         <f aca="false">B94*(1-$B$96)</f>
-        <v>54.4400424947561</v>
+        <v>54.4400424947562</v>
       </c>
       <c r="C102" s="16" t="n">
         <f aca="false">C94*(1-$B$96)</f>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="D102" s="16" t="n">
         <f aca="false">D94*(1-$B$96)</f>
-        <v>24.5775870559767</v>
+        <v>24.5775870559768</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45573,7 +45573,7 @@
       </c>
       <c r="B103" s="27" t="n">
         <f aca="false">SUMPRODUCT(B97:B102,1/(1+tp_r)^{1;2;3;4;5;6})+B102*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>735.153742284008</v>
+        <v>735.153742284009</v>
       </c>
       <c r="C103" s="27" t="n">
         <f aca="false">SUMPRODUCT(C97:C102,1/(1+tp_r)^{1;2;3;4;5;6})+C102*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -45593,11 +45593,11 @@
       </c>
       <c r="B104" s="27" t="n">
         <f aca="false">B103*(1+tp_r)</f>
-        <v>808.669116512409</v>
+        <v>808.66911651241</v>
       </c>
       <c r="C104" s="27" t="n">
         <f aca="false">C103*(1+tp_r)</f>
-        <v>641.696625371716</v>
+        <v>641.696625371717</v>
       </c>
       <c r="D104" s="27" t="n">
         <f aca="false">D103*(1+tp_r)</f>
@@ -45801,7 +45801,7 @@
       </c>
       <c r="B120" s="30" t="n">
         <f aca="false">tp_w_dcf*B105+(1-tp_w_dcf)*B116</f>
-        <v>566.562292345012</v>
+        <v>566.562292345013</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>609</v>
@@ -45837,7 +45837,7 @@
       </c>
       <c r="B123" s="15" t="n">
         <f aca="false">B120/px-1</f>
-        <v>0.75951022467395</v>
+        <v>0.759510224673953</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>614</v>
@@ -45849,7 +45849,7 @@
       </c>
       <c r="B124" s="15" t="n">
         <f aca="false">B121/px-1</f>
-        <v>0.518204879818955</v>
+        <v>0.518204879818957</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="B125" s="15" t="n">
         <f aca="false">B115/cons_feps-1</f>
-        <v>0.505517723688232</v>
+        <v>0.505517723688234</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>617</v>
@@ -46182,7 +46182,7 @@
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">C7/B7-1</f>
-        <v>0.0938819451407307</v>
+        <v>0.093881945140732</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">PL!E116</f>
@@ -46190,7 +46190,7 @@
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">E7/B7-1</f>
-        <v>0.0938819451407307</v>
+        <v>0.093881945140732</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">PL!E155</f>
@@ -46198,7 +46198,7 @@
       </c>
       <c r="H7" s="15" t="n">
         <f aca="false">G7/B7-1</f>
-        <v>0.0938819451407307</v>
+        <v>0.093881945140732</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>643</v>
@@ -46218,7 +46218,7 @@
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.0774545214313749</v>
+        <v>0.077454521431376</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">PL!E116</f>
@@ -46226,7 +46226,7 @@
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>0.0774545214313749</v>
+        <v>0.077454521431376</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">PL!E155</f>
@@ -46234,7 +46234,7 @@
       </c>
       <c r="H8" s="15" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>0.0774545214313749</v>
+        <v>0.077454521431376</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>648</v>
@@ -46250,27 +46250,27 @@
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">PL!E95</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.373607441783937</v>
+        <v>0.373607441783939</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">PL!E134</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>0.373607441783937</v>
+        <v>0.373607441783939</v>
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">PL!E173</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="H9" s="15" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>0.373607441783937</v>
+        <v>0.373607441783939</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>643</v>
@@ -46286,27 +46286,27 @@
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">PL!E95</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.359053794846993</v>
+        <v>0.359053794846994</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">PL!E134</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F10" s="15" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.359053794846993</v>
+        <v>0.359053794846994</v>
       </c>
       <c r="G10" s="21" t="n">
         <f aca="false">PL!E173</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="H10" s="15" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>0.359053794846993</v>
+        <v>0.359053794846994</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>648</v>
@@ -46329,7 +46329,7 @@
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">C11-B11</f>
-        <v>0.00163363853259608</v>
+        <v>0.00163363853259607</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">PL!E125</f>
@@ -46337,7 +46337,7 @@
       </c>
       <c r="F11" s="15" t="n">
         <f aca="false">E11-B11</f>
-        <v>0.00163363853259608</v>
+        <v>0.00163363853259607</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">PL!E164</f>
@@ -46345,7 +46345,7 @@
       </c>
       <c r="H11" s="15" t="n">
         <f aca="false">G11-B11</f>
-        <v>0.00163363853259608</v>
+        <v>0.00163363853259607</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>643</v>
@@ -46360,15 +46360,15 @@
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">PL!E78</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">PL!E117</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">PL!E156</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>111</v>
@@ -46393,7 +46393,7 @@
       </c>
       <c r="D14" s="15" t="n">
         <f aca="false">C14-B14</f>
-        <v>-0.203896518164716</v>
+        <v>-0.203896518164715</v>
       </c>
       <c r="E14" s="15" t="n">
         <f aca="false">PL!D108</f>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="F14" s="15" t="n">
         <f aca="false">E14-B14</f>
-        <v>-0.203896518164716</v>
+        <v>-0.203896518164715</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="false">PL!D147</f>
@@ -46409,7 +46409,7 @@
       </c>
       <c r="H14" s="15" t="n">
         <f aca="false">G14-B14</f>
-        <v>-0.203896518164716</v>
+        <v>-0.203896518164715</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>657</v>
@@ -46424,15 +46424,15 @@
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">PL!D80</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">PL!D119</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="G15" s="16" t="n">
         <f aca="false">PL!D158</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>111</v>
@@ -46526,7 +46526,7 @@
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">C20-B20</f>
-        <v>-0.000997082836643792</v>
+        <v>-0.000997082836643799</v>
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">PL!E125</f>
@@ -46534,7 +46534,7 @@
       </c>
       <c r="F20" s="15" t="n">
         <f aca="false">E20-B20</f>
-        <v>-0.000997082836643792</v>
+        <v>-0.000997082836643799</v>
       </c>
       <c r="G20" s="11" t="n">
         <f aca="false">PL!E164</f>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="H20" s="15" t="n">
         <f aca="false">G20-B20</f>
-        <v>-0.000997082836643792</v>
+        <v>-0.000997082836643799</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>669</v>
@@ -46603,7 +46603,7 @@
       </c>
       <c r="D26" s="15" t="n">
         <f aca="false">C26/B26-1</f>
-        <v>0.505517723688232</v>
+        <v>0.505517723688234</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>295</v>
@@ -46622,11 +46622,11 @@
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">Val!B120</f>
-        <v>566.562292345012</v>
+        <v>566.562292345013</v>
       </c>
       <c r="D27" s="15" t="n">
         <f aca="false">C27/B27-1</f>
-        <v>0.324238716214033</v>
+        <v>0.324238716214035</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>291</v>
@@ -46649,7 +46649,7 @@
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">C28/B28-1</f>
-        <v>0.14262801818835</v>
+        <v>0.142628018188351</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>38</v>
@@ -46746,7 +46746,7 @@
       </c>
       <c r="F4" s="16" t="n">
         <f aca="false">PL!E95</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="G4" s="15" t="n">
         <f aca="false">F4/F$4-1</f>
@@ -46754,11 +46754,11 @@
       </c>
       <c r="H4" s="19" t="n">
         <f aca="false">PL!F77</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I4" s="19" t="n">
         <f aca="false">PL!F74</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J4" s="11" t="n">
         <f aca="false">PL!F86</f>
@@ -46766,7 +46766,7 @@
       </c>
       <c r="K4" s="16" t="n">
         <f aca="false">PL!F95</f>
-        <v>51.9245329868023</v>
+        <v>51.9245329868024</v>
       </c>
       <c r="L4" s="15" t="n">
         <f aca="false">K4/K$4-1</f>
@@ -46782,11 +46782,11 @@
       </c>
       <c r="C5" s="19" t="n">
         <f aca="false">E57</f>
-        <v>5051.62908864834</v>
+        <v>5051.62908864835</v>
       </c>
       <c r="D5" s="19" t="n">
         <f aca="false">E54</f>
-        <v>3733.65262464834</v>
+        <v>3733.65262464835</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">E66</f>
@@ -46794,7 +46794,7 @@
       </c>
       <c r="F5" s="16" t="n">
         <f aca="false">E75</f>
-        <v>38.1217140638485</v>
+        <v>38.1217140638486</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">F5/F$4-1</f>
@@ -46814,7 +46814,7 @@
       </c>
       <c r="K5" s="16" t="n">
         <f aca="false">F75</f>
-        <v>42.4634575768041</v>
+        <v>42.4634575768042</v>
       </c>
       <c r="L5" s="15" t="n">
         <f aca="false">K5/K$4-1</f>
@@ -46846,7 +46846,7 @@
       </c>
       <c r="G6" s="15" t="n">
         <f aca="false">F6/F$4-1</f>
-        <v>0.08392671200469</v>
+        <v>0.0839267120046903</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">F96</f>
@@ -46862,11 +46862,11 @@
       </c>
       <c r="K6" s="16" t="n">
         <f aca="false">F114</f>
-        <v>59.0664482683204</v>
+        <v>59.0664482683205</v>
       </c>
       <c r="L6" s="15" t="n">
         <f aca="false">K6/K$4-1</f>
-        <v>0.137544140904133</v>
+        <v>0.137544140904134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46890,11 +46890,11 @@
       </c>
       <c r="F7" s="16" t="n">
         <f aca="false">E153</f>
-        <v>43.272714363568</v>
+        <v>43.2727143635681</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">F7/F$4-1</f>
-        <v>-0.00778046479920314</v>
+        <v>-0.0077804647992028</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">F135</f>
@@ -46914,7 +46914,7 @@
       </c>
       <c r="L7" s="15" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.0108923395686272</v>
+        <v>-0.0108923395686275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46938,19 +46938,19 @@
       </c>
       <c r="F8" s="16" t="n">
         <f aca="false">E192</f>
-        <v>44.1210191462479</v>
+        <v>44.121019146248</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="false">F8/F$4-1</f>
-        <v>0.0116706971988045</v>
+        <v>0.0116706971988048</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">F174</f>
-        <v>4870.76626498278</v>
+        <v>4870.76626498279</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">F171</f>
-        <v>3526.43027170278</v>
+        <v>3526.43027170279</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">F183</f>
@@ -46990,15 +46990,15 @@
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.0202064734053272</v>
+        <v>-0.0202064734053276</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">F213</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">F210</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">F222</f>
@@ -47006,7 +47006,7 @@
       </c>
       <c r="K9" s="16" t="n">
         <f aca="false">F231</f>
-        <v>49.8020781368128</v>
+        <v>49.8020781368129</v>
       </c>
       <c r="L9" s="15" t="n">
         <f aca="false">K9/K$4-1</f>
@@ -47034,23 +47034,23 @@
       </c>
       <c r="F10" s="16" t="n">
         <f aca="false">E270</f>
-        <v>44.052659002228</v>
+        <v>44.0526590022281</v>
       </c>
       <c r="G10" s="15" t="n">
         <f aca="false">F10/F$4-1</f>
-        <v>0.0101032367026634</v>
+        <v>0.0101032367026639</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">F252</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">F249</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J10" s="11" t="n">
         <f aca="false">F261</f>
-        <v>0.0531660277163988</v>
+        <v>0.0531660277163987</v>
       </c>
       <c r="K10" s="16" t="n">
         <f aca="false">F270</f>
@@ -47058,7 +47058,7 @@
       </c>
       <c r="L10" s="15" t="n">
         <f aca="false">K10/K$4-1</f>
-        <v>0.0204378809774655</v>
+        <v>0.020437880977465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47082,7 +47082,7 @@
       </c>
       <c r="F11" s="16" t="n">
         <f aca="false">E309</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">F11/F$4-1</f>
@@ -47102,7 +47102,7 @@
       </c>
       <c r="K11" s="16" t="n">
         <f aca="false">F309</f>
-        <v>44.5645352051176</v>
+        <v>44.5645352051177</v>
       </c>
       <c r="L11" s="15" t="n">
         <f aca="false">K11/K$4-1</f>
@@ -47130,7 +47130,7 @@
       </c>
       <c r="F12" s="16" t="n">
         <f aca="false">E348</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">F12/F$4-1</f>
@@ -47138,11 +47138,11 @@
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">F330</f>
-        <v>6986.62442800445</v>
+        <v>6986.62442800446</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">F327</f>
-        <v>5642.28843472445</v>
+        <v>5642.28843472446</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">F339</f>
@@ -47154,7 +47154,7 @@
       </c>
       <c r="L12" s="15" t="n">
         <f aca="false">K12/K$4-1</f>
-        <v>0.17655497891585</v>
+        <v>0.176554978915849</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47166,11 +47166,11 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">E369</f>
-        <v>4832.00246366903</v>
+        <v>4832.00246366904</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">E366</f>
-        <v>3514.02599966903</v>
+        <v>3514.02599966904</v>
       </c>
       <c r="E13" s="11" t="n">
         <f aca="false">E378</f>
@@ -47226,19 +47226,19 @@
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">E426</f>
-        <v>50.9324658936953</v>
+        <v>50.9324658936954</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="false">F14/F$4-1</f>
-        <v>0.16785342400938</v>
+        <v>0.167853424009381</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">F408</f>
-        <v>6986.62442800445</v>
+        <v>6986.62442800446</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">F405</f>
-        <v>5642.28843472445</v>
+        <v>5642.28843472446</v>
       </c>
       <c r="J14" s="11" t="n">
         <f aca="false">F417</f>
@@ -47246,7 +47246,7 @@
       </c>
       <c r="K14" s="16" t="n">
         <f aca="false">F426</f>
-        <v>60.8751595174091</v>
+        <v>60.8751595174092</v>
       </c>
       <c r="L14" s="15" t="n">
         <f aca="false">K14/K$4-1</f>
@@ -47274,7 +47274,7 @@
       </c>
       <c r="F15" s="16" t="n">
         <f aca="false">E465</f>
-        <v>42.3230942426171</v>
+        <v>42.3230942426172</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">F15/F$4-1</f>
@@ -47282,11 +47282,11 @@
       </c>
       <c r="H15" s="19" t="n">
         <f aca="false">F447</f>
-        <v>5856.73592093704</v>
+        <v>5856.73592093705</v>
       </c>
       <c r="I15" s="19" t="n">
         <f aca="false">F444</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J15" s="11" t="n">
         <f aca="false">F456</f>
@@ -47294,11 +47294,11 @@
       </c>
       <c r="K15" s="16" t="n">
         <f aca="false">F465</f>
-        <v>49.5102865044814</v>
+        <v>49.5102865044815</v>
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.046495295064754</v>
+        <v>-0.0464952950647543</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47330,11 +47330,11 @@
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">F486</f>
-        <v>6166.78028717704</v>
+        <v>6166.78028717705</v>
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">F483</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J16" s="11" t="n">
         <f aca="false">F495</f>
@@ -47342,11 +47342,11 @@
       </c>
       <c r="K16" s="16" t="n">
         <f aca="false">F504</f>
-        <v>53.4614364288283</v>
+        <v>53.4614364288284</v>
       </c>
       <c r="L16" s="15" t="n">
         <f aca="false">K16/K$4-1</f>
-        <v>0.0295987918161276</v>
+        <v>0.0295987918161273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47374,15 +47374,15 @@
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0501648748927406</v>
+        <v>-0.0501648748927407</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">F525</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">F522</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J17" s="11" t="n">
         <f aca="false">F534</f>
@@ -47418,19 +47418,19 @@
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">E582</f>
-        <v>45.7998286202753</v>
+        <v>45.7998286202754</v>
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">F18/F$4-1</f>
-        <v>0.0501648748927404</v>
+        <v>0.0501648748927408</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">F564</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">F561</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J18" s="11" t="n">
         <f aca="false">F573</f>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="L18" s="15" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>0.0602241310520513</v>
+        <v>0.060224131052051</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47466,19 +47466,19 @@
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">E621</f>
-        <v>40.3591751534559</v>
+        <v>40.359175153456</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">F19/F$4-1</f>
-        <v>-0.0745863160928899</v>
+        <v>-0.0745863160928896</v>
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">F603</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">F600</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J19" s="11" t="n">
         <f aca="false">F612</f>
@@ -47486,7 +47486,7 @@
       </c>
       <c r="K19" s="16" t="n">
         <f aca="false">F621</f>
-        <v>48.0468885855885</v>
+        <v>48.0468885855886</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">K19/K$4-1</f>
@@ -47522,11 +47522,11 @@
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">F642</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I20" s="19" t="n">
         <f aca="false">F639</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J20" s="11" t="n">
         <f aca="false">F651</f>
@@ -47534,7 +47534,7 @@
       </c>
       <c r="K20" s="16" t="n">
         <f aca="false">F660</f>
-        <v>55.8021773880161</v>
+        <v>55.8021773880162</v>
       </c>
       <c r="L20" s="15" t="n">
         <f aca="false">K20/K$4-1</f>
@@ -47566,15 +47566,15 @@
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">F21/F$4-1</f>
-        <v>-0.0587672065342775</v>
+        <v>-0.0587672065342774</v>
       </c>
       <c r="H21" s="19" t="n">
         <f aca="false">F681</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I21" s="19" t="n">
         <f aca="false">F678</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">F690</f>
@@ -47582,11 +47582,11 @@
       </c>
       <c r="K21" s="16" t="n">
         <f aca="false">F699</f>
-        <v>49.2108932287832</v>
+        <v>49.2108932287833</v>
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">K21/K$4-1</f>
-        <v>-0.052261226089579</v>
+        <v>-0.0522612260895791</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47618,11 +47618,11 @@
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">F720</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="I22" s="19" t="n">
         <f aca="false">F717</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">F729</f>
@@ -47658,7 +47658,7 @@
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">PL!E134</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="G23" s="15" t="n">
         <f aca="false">F23/F$4-1</f>
@@ -47678,7 +47678,7 @@
       </c>
       <c r="K23" s="16" t="n">
         <f aca="false">PL!F134</f>
-        <v>41.9645280138805</v>
+        <v>41.9645280138806</v>
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">K23/K$4-1</f>
@@ -47706,7 +47706,7 @@
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">PL!E173</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="G24" s="15" t="n">
         <f aca="false">F24/F$4-1</f>
@@ -47726,7 +47726,7 @@
       </c>
       <c r="K24" s="16" t="n">
         <f aca="false">PL!F173</f>
-        <v>31.5644992489321</v>
+        <v>31.5644992489322</v>
       </c>
       <c r="L24" s="15" t="n">
         <f aca="false">K24/K$4-1</f>
@@ -47783,7 +47783,7 @@
       </c>
       <c r="D43" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -47882,7 +47882,7 @@
       </c>
       <c r="D47" s="19" t="n">
         <f aca="false">D45*D46</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E47" s="19" t="n">
         <f aca="false">E45*E46</f>
@@ -47906,7 +47906,7 @@
       </c>
       <c r="D48" s="19" t="n">
         <f aca="false">D47*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E48" s="19" t="n">
         <f aca="false">E47*fx</f>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="G51" s="15" t="n">
         <f aca="false">$D$49*G50</f>
-        <v>0.0937272867830269</v>
+        <v>0.093727286783027</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48001,7 +48001,7 @@
       </c>
       <c r="F52" s="19" t="n">
         <f aca="false">F48*F51</f>
-        <v>4640.03983118787</v>
+        <v>4640.03983118788</v>
       </c>
       <c r="G52" s="19" t="n">
         <f aca="false">G48*G51</f>
@@ -48052,7 +48052,7 @@
       </c>
       <c r="E54" s="19" t="n">
         <f aca="false">E52*(1-E53)</f>
-        <v>3733.65262464834</v>
+        <v>3733.65262464835</v>
       </c>
       <c r="F54" s="19" t="n">
         <f aca="false">F52*(1-F53)</f>
@@ -48113,7 +48113,7 @@
       </c>
       <c r="E57" s="19" t="n">
         <f aca="false">E54+E56</f>
-        <v>5051.62908864834</v>
+        <v>5051.62908864835</v>
       </c>
       <c r="F57" s="19" t="n">
         <f aca="false">F54+F56</f>
@@ -48137,11 +48137,11 @@
       </c>
       <c r="E58" s="15" t="n">
         <f aca="false">E57/D57-1</f>
-        <v>0.263313111499155</v>
+        <v>0.263313111499156</v>
       </c>
       <c r="F58" s="15" t="n">
         <f aca="false">F57/E57-1</f>
-        <v>0.000938067601321535</v>
+        <v>0.000938067601321757</v>
       </c>
       <c r="G58" s="15" t="n">
         <f aca="false">G57/F57-1</f>
@@ -48165,7 +48165,7 @@
       </c>
       <c r="E59" s="15" t="n">
         <f aca="false">E54/E57</f>
-        <v>0.73909872619871</v>
+        <v>0.739098726198711</v>
       </c>
       <c r="F59" s="15" t="n">
         <f aca="false">F54/F57</f>
@@ -48185,7 +48185,7 @@
       </c>
       <c r="D60" s="16" t="n">
         <f aca="false">D54/fx/D45</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E60" s="16" t="n">
         <f aca="false">E54/fx/E45</f>
@@ -48217,11 +48217,11 @@
       </c>
       <c r="F61" s="19" t="n">
         <f aca="false">F52/fx/odm_vr</f>
-        <v>21.481665885129</v>
+        <v>21.4816658851291</v>
       </c>
       <c r="G61" s="19" t="n">
         <f aca="false">G52/fx/odm_vr</f>
-        <v>22.8396127432992</v>
+        <v>22.8396127432993</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>418</v>
@@ -48264,7 +48264,7 @@
       </c>
       <c r="F64" s="21" t="n">
         <f aca="false">($D$63+d_ai+vrd)*F52*(1-F53*(1-keep))</f>
-        <v>182.93870659888</v>
+        <v>182.938706598881</v>
       </c>
       <c r="G64" s="21" t="n">
         <f aca="false">($D$63+d_ai+vrd)*G52*(1-G53*(1-keep))</f>
@@ -48295,11 +48295,11 @@
       </c>
       <c r="F65" s="19" t="n">
         <f aca="false">$D$63*F56+F64</f>
-        <v>267.942041216608</v>
+        <v>267.942041216609</v>
       </c>
       <c r="G65" s="19" t="n">
         <f aca="false">$D$63*G56+G64</f>
-        <v>280.214074023929</v>
+        <v>280.21407402393</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48378,7 +48378,7 @@
       </c>
       <c r="F68" s="19" t="n">
         <f aca="false">E68*(1+MAX(0,phi*F58))</f>
-        <v>78.7169362156545</v>
+        <v>78.7169362156546</v>
       </c>
       <c r="G68" s="19" t="n">
         <f aca="false">F68*(1+MAX(0,phi*G58))</f>
@@ -48406,7 +48406,7 @@
       </c>
       <c r="F69" s="19" t="n">
         <f aca="false">F68+0*F57</f>
-        <v>78.7169362156545</v>
+        <v>78.7169362156546</v>
       </c>
       <c r="G69" s="19" t="n">
         <f aca="false">G68+0*G57</f>
@@ -48438,7 +48438,7 @@
       </c>
       <c r="G70" s="19" t="n">
         <f aca="false">G65-G69</f>
-        <v>201.404526851042</v>
+        <v>201.404526851043</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48514,7 +48514,7 @@
       </c>
       <c r="E73" s="19" t="n">
         <f aca="false">E70*E72</f>
-        <v>146.944023893442</v>
+        <v>146.944023893443</v>
       </c>
       <c r="F73" s="19" t="n">
         <f aca="false">F70*F72</f>
@@ -48570,15 +48570,15 @@
       </c>
       <c r="E75" s="21" t="n">
         <f aca="false">E73/E74</f>
-        <v>38.1217140638485</v>
+        <v>38.1217140638486</v>
       </c>
       <c r="F75" s="21" t="n">
         <f aca="false">F73/F74</f>
-        <v>42.4634575768041</v>
+        <v>42.4634575768042</v>
       </c>
       <c r="G75" s="21" t="n">
         <f aca="false">G73/G74</f>
-        <v>45.1966063470935</v>
+        <v>45.1966063470936</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48594,7 +48594,7 @@
       </c>
       <c r="E76" s="15" t="n">
         <f aca="false">E75/D75-1</f>
-        <v>0.327243706551064</v>
+        <v>0.327243706551065</v>
       </c>
       <c r="F76" s="15" t="n">
         <f aca="false">F75/E75-1</f>
@@ -48650,7 +48650,7 @@
       </c>
       <c r="D82" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E82" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48749,7 +48749,7 @@
       </c>
       <c r="D86" s="19" t="n">
         <f aca="false">D84*D85</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E86" s="19" t="n">
         <f aca="false">E84*E85</f>
@@ -48773,7 +48773,7 @@
       </c>
       <c r="D87" s="19" t="n">
         <f aca="false">D86*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E87" s="19" t="n">
         <f aca="false">E86*fx</f>
@@ -48864,15 +48864,15 @@
       </c>
       <c r="E91" s="19" t="n">
         <f aca="false">E87*E90</f>
-        <v>5368.65083282768</v>
+        <v>5368.65083282769</v>
       </c>
       <c r="F91" s="19" t="n">
         <f aca="false">F87*F90</f>
-        <v>6805.39175240888</v>
+        <v>6805.39175240889</v>
       </c>
       <c r="G91" s="19" t="n">
         <f aca="false">G87*G90</f>
-        <v>7752.41712543986</v>
+        <v>7752.41712543987</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48927,7 +48927,7 @@
       </c>
       <c r="G93" s="19" t="n">
         <f aca="false">G91*(1-G92)</f>
-        <v>5814.31284407989</v>
+        <v>5814.3128440799</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48988,7 +48988,7 @@
       </c>
       <c r="G96" s="19" t="n">
         <f aca="false">G93+G95</f>
-        <v>7185.53555722549</v>
+        <v>7185.5355572255</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49004,7 +49004,7 @@
       </c>
       <c r="E97" s="15" t="n">
         <f aca="false">E96/D96-1</f>
-        <v>0.53793461488126</v>
+        <v>0.537934614881261</v>
       </c>
       <c r="F97" s="15" t="n">
         <f aca="false">F96/E96-1</f>
@@ -49012,7 +49012,7 @@
       </c>
       <c r="G97" s="15" t="n">
         <f aca="false">G96/F96-1</f>
-        <v>0.0584631992187716</v>
+        <v>0.0584631992187719</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49052,15 +49052,15 @@
       </c>
       <c r="D99" s="16" t="n">
         <f aca="false">D93/fx/D84</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E99" s="16" t="n">
         <f aca="false">E93/fx/E84</f>
-        <v>3.6255709579922</v>
+        <v>3.62557095799221</v>
       </c>
       <c r="F99" s="16" t="n">
         <f aca="false">F93/fx/F84</f>
-        <v>3.22272974043751</v>
+        <v>3.22272974043752</v>
       </c>
       <c r="G99" s="16" t="n">
         <f aca="false">G93/fx/G84</f>
@@ -49080,7 +49080,7 @@
       </c>
       <c r="E100" s="19" t="n">
         <f aca="false">E91/fx/odm_vr</f>
-        <v>24.8548649667948</v>
+        <v>24.8548649667949</v>
       </c>
       <c r="F100" s="19" t="n">
         <f aca="false">F91/fx/odm_vr</f>
@@ -49088,7 +49088,7 @@
       </c>
       <c r="G100" s="19" t="n">
         <f aca="false">G91/fx/odm_vr</f>
-        <v>35.8908200251845</v>
+        <v>35.8908200251846</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>418</v>
@@ -49241,7 +49241,7 @@
       </c>
       <c r="E107" s="19" t="n">
         <f aca="false">D107*(1+MAX(0,phi*E97))</f>
-        <v>86.5074635717704</v>
+        <v>86.5074635717705</v>
       </c>
       <c r="F107" s="19" t="n">
         <f aca="false">E107*(1+MAX(0,phi*F97))</f>
@@ -49249,7 +49249,7 @@
       </c>
       <c r="G107" s="19" t="n">
         <f aca="false">F107*(1+MAX(0,phi*G97))</f>
-        <v>92.2093699168205</v>
+        <v>92.2093699168206</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49269,7 +49269,7 @@
       </c>
       <c r="E108" s="19" t="n">
         <f aca="false">E107+0*E96</f>
-        <v>86.5074635717704</v>
+        <v>86.5074635717705</v>
       </c>
       <c r="F108" s="19" t="n">
         <f aca="false">F107+0*F96</f>
@@ -49277,7 +49277,7 @@
       </c>
       <c r="G108" s="19" t="n">
         <f aca="false">G107+0*G96</f>
-        <v>92.2093699168205</v>
+        <v>92.2093699168206</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49297,7 +49297,7 @@
       </c>
       <c r="E109" s="19" t="n">
         <f aca="false">E104-E108</f>
-        <v>210.653987821015</v>
+        <v>210.653987821016</v>
       </c>
       <c r="F109" s="19" t="n">
         <f aca="false">F104-F108</f>
@@ -49381,7 +49381,7 @@
       </c>
       <c r="E112" s="19" t="n">
         <f aca="false">E109*E111</f>
-        <v>182.215699465178</v>
+        <v>182.215699465179</v>
       </c>
       <c r="F112" s="19" t="n">
         <f aca="false">F109*F111</f>
@@ -49441,11 +49441,11 @@
       </c>
       <c r="F114" s="21" t="n">
         <f aca="false">F112/F113</f>
-        <v>59.0664482683204</v>
+        <v>59.0664482683205</v>
       </c>
       <c r="G114" s="21" t="n">
         <f aca="false">G112/G113</f>
-        <v>67.0039734685072</v>
+        <v>67.0039734685073</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49461,11 +49461,11 @@
       </c>
       <c r="E115" s="15" t="n">
         <f aca="false">E114/D114-1</f>
-        <v>0.645828349748566</v>
+        <v>0.645828349748568</v>
       </c>
       <c r="F115" s="15" t="n">
         <f aca="false">F114/E114-1</f>
-        <v>0.249495145934637</v>
+        <v>0.249495145934638</v>
       </c>
       <c r="G115" s="15" t="n">
         <f aca="false">G114/F114-1</f>
@@ -49517,7 +49517,7 @@
       </c>
       <c r="D121" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E121" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49616,7 +49616,7 @@
       </c>
       <c r="D125" s="19" t="n">
         <f aca="false">D123*D124</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E125" s="19" t="n">
         <f aca="false">E123*E124</f>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="D126" s="19" t="n">
         <f aca="false">D125*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E126" s="19" t="n">
         <f aca="false">E125*fx</f>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="G129" s="15" t="n">
         <f aca="false">$D$127*G128</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49739,7 +49739,7 @@
       </c>
       <c r="G130" s="19" t="n">
         <f aca="false">G126*G129</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49794,7 +49794,7 @@
       </c>
       <c r="G132" s="19" t="n">
         <f aca="false">G130*(1-G131)</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49855,7 +49855,7 @@
       </c>
       <c r="G135" s="19" t="n">
         <f aca="false">G132+G134</f>
-        <v>7714.10945214185</v>
+        <v>7714.10945214186</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49871,7 +49871,7 @@
       </c>
       <c r="E136" s="15" t="n">
         <f aca="false">E135/D135-1</f>
-        <v>0.550140015031575</v>
+        <v>0.550140015031577</v>
       </c>
       <c r="F136" s="15" t="n">
         <f aca="false">F135/E135-1</f>
@@ -49919,19 +49919,19 @@
       </c>
       <c r="D138" s="16" t="n">
         <f aca="false">D132/fx/D123</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E138" s="16" t="n">
         <f aca="false">E132/fx/E123</f>
-        <v>3.66219288686081</v>
+        <v>3.66219288686082</v>
       </c>
       <c r="F138" s="16" t="n">
         <f aca="false">F132/fx/F123</f>
-        <v>3.47908324251777</v>
+        <v>3.47908324251778</v>
       </c>
       <c r="G138" s="16" t="n">
         <f aca="false">G132/fx/G123</f>
-        <v>3.29597359817473</v>
+        <v>3.29597359817474</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49951,7 +49951,7 @@
       </c>
       <c r="F139" s="19" t="n">
         <f aca="false">F130/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G139" s="19" t="n">
         <f aca="false">G130/fx/odm_vr</f>
@@ -49994,7 +49994,7 @@
       </c>
       <c r="E142" s="21" t="n">
         <f aca="false">($D$141+d_ai+vrd)*E130*(1-E131*(1-keep))</f>
-        <v>196.349723440207</v>
+        <v>196.349723440208</v>
       </c>
       <c r="F142" s="21" t="n">
         <f aca="false">($D$141+d_ai+vrd)*F130*(1-F131*(1-keep))</f>
@@ -50025,7 +50025,7 @@
       </c>
       <c r="E143" s="19" t="n">
         <f aca="false">$D$141*E134+E142</f>
-        <v>279.686326006607</v>
+        <v>279.686326006608</v>
       </c>
       <c r="F143" s="19" t="n">
         <f aca="false">$D$141*F134+F142</f>
@@ -50112,11 +50112,11 @@
       </c>
       <c r="F146" s="19" t="n">
         <f aca="false">E146*(1+MAX(0,phi*F136))</f>
-        <v>92.5896270633237</v>
+        <v>92.5896270633238</v>
       </c>
       <c r="G146" s="19" t="n">
         <f aca="false">F146*(1+MAX(0,phi*G136))</f>
-        <v>95.11479710905</v>
+        <v>95.1147971090501</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50140,11 +50140,11 @@
       </c>
       <c r="F147" s="19" t="n">
         <f aca="false">F146+0*F135</f>
-        <v>92.5896270633237</v>
+        <v>92.5896270633238</v>
       </c>
       <c r="G147" s="19" t="n">
         <f aca="false">G146+0*G135</f>
-        <v>95.11479710905</v>
+        <v>95.1147971090501</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50168,7 +50168,7 @@
       </c>
       <c r="F148" s="19" t="n">
         <f aca="false">F143-F147</f>
-        <v>228.86509703595</v>
+        <v>228.865097035951</v>
       </c>
       <c r="G148" s="19" t="n">
         <f aca="false">G143-G147</f>
@@ -50192,7 +50192,7 @@
       </c>
       <c r="E149" s="11" t="n">
         <f aca="false">E148/E135</f>
-        <v>0.0311090078342452</v>
+        <v>0.0311090078342453</v>
       </c>
       <c r="F149" s="11" t="n">
         <f aca="false">F148/F135</f>
@@ -50304,7 +50304,7 @@
       </c>
       <c r="E153" s="21" t="n">
         <f aca="false">E151/E152</f>
-        <v>43.272714363568</v>
+        <v>43.2727143635681</v>
       </c>
       <c r="F153" s="21" t="n">
         <f aca="false">F151/F152</f>
@@ -50312,7 +50312,7 @@
       </c>
       <c r="G153" s="21" t="n">
         <f aca="false">G151/G152</f>
-        <v>55.3763827014454</v>
+        <v>55.3763827014455</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50328,7 +50328,7 @@
       </c>
       <c r="E154" s="15" t="n">
         <f aca="false">E153/D153-1</f>
-        <v>0.506580677569602</v>
+        <v>0.506580677569604</v>
       </c>
       <c r="F154" s="15" t="n">
         <f aca="false">F153/E153-1</f>
@@ -50384,7 +50384,7 @@
       </c>
       <c r="D160" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E160" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="D164" s="19" t="n">
         <f aca="false">D162*D163</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E164" s="19" t="n">
         <f aca="false">E162*E163</f>
@@ -50507,7 +50507,7 @@
       </c>
       <c r="D165" s="19" t="n">
         <f aca="false">D164*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E165" s="19" t="n">
         <f aca="false">E164*fx</f>
@@ -50582,7 +50582,7 @@
       </c>
       <c r="G168" s="15" t="n">
         <f aca="false">$D$166*G167</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50606,7 +50606,7 @@
       </c>
       <c r="G169" s="19" t="n">
         <f aca="false">G165*G168</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50657,11 +50657,11 @@
       </c>
       <c r="F171" s="19" t="n">
         <f aca="false">F169*(1-F170)</f>
-        <v>3526.43027170278</v>
+        <v>3526.43027170279</v>
       </c>
       <c r="G171" s="19" t="n">
         <f aca="false">G169*(1-G170)</f>
-        <v>3171.44336949812</v>
+        <v>3171.44336949813</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50718,11 +50718,11 @@
       </c>
       <c r="F174" s="19" t="n">
         <f aca="false">F171+F173</f>
-        <v>4870.76626498278</v>
+        <v>4870.76626498279</v>
       </c>
       <c r="G174" s="19" t="n">
         <f aca="false">G171+G173</f>
-        <v>4542.66608264372</v>
+        <v>4542.66608264373</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="E175" s="15" t="n">
         <f aca="false">E174/D174-1</f>
-        <v>0.245005011273681</v>
+        <v>0.245005011273683</v>
       </c>
       <c r="F175" s="15" t="n">
         <f aca="false">F174/E174-1</f>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="G175" s="15" t="n">
         <f aca="false">G174/F174-1</f>
-        <v>-0.0673611018245439</v>
+        <v>-0.0673611018245442</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50786,7 +50786,7 @@
       </c>
       <c r="D177" s="16" t="n">
         <f aca="false">D171/fx/D162</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E177" s="16" t="n">
         <f aca="false">E171/fx/E162</f>
@@ -50794,7 +50794,7 @@
       </c>
       <c r="F177" s="16" t="n">
         <f aca="false">F171/fx/F162</f>
-        <v>2.08744994551066</v>
+        <v>2.08744994551067</v>
       </c>
       <c r="G177" s="16" t="n">
         <f aca="false">G171/fx/G162</f>
@@ -50818,7 +50818,7 @@
       </c>
       <c r="F178" s="19" t="n">
         <f aca="false">F169/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G178" s="19" t="n">
         <f aca="false">G169/fx/odm_vr</f>
@@ -50869,7 +50869,7 @@
       </c>
       <c r="G181" s="21" t="n">
         <f aca="false">($D$180+d_ai+vrd)*G169*(1-G170*(1-keep))</f>
-        <v>242.419963619544</v>
+        <v>242.419963619545</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>423</v>
@@ -50892,7 +50892,7 @@
       </c>
       <c r="E182" s="19" t="n">
         <f aca="false">$D$180*E173+E181</f>
-        <v>274.777582920602</v>
+        <v>274.777582920603</v>
       </c>
       <c r="F182" s="19" t="n">
         <f aca="false">$D$180*F173+F181</f>
@@ -50952,7 +50952,7 @@
       </c>
       <c r="G184" s="11" t="n">
         <f aca="false">G181/G171</f>
-        <v>0.0764383706015558</v>
+        <v>0.0764383706015557</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>425</v>
@@ -50975,15 +50975,15 @@
       </c>
       <c r="E185" s="19" t="n">
         <f aca="false">D185*(1+MAX(0,phi*E175))</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
       <c r="F185" s="19" t="n">
         <f aca="false">E185*(1+MAX(0,phi*F175))</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
       <c r="G185" s="19" t="n">
         <f aca="false">F185*(1+MAX(0,phi*G175))</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51003,15 +51003,15 @@
       </c>
       <c r="E186" s="19" t="n">
         <f aca="false">E185+0*E174</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
       <c r="F186" s="19" t="n">
         <f aca="false">F185+0*F174</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
       <c r="G186" s="19" t="n">
         <f aca="false">G185+0*G174</f>
-        <v>78.1660737047715</v>
+        <v>78.1660737047716</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51039,7 +51039,7 @@
       </c>
       <c r="G187" s="19" t="n">
         <f aca="false">G182-G186</f>
-        <v>250.957291224855</v>
+        <v>250.957291224856</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51171,7 +51171,7 @@
       </c>
       <c r="E192" s="21" t="n">
         <f aca="false">E190/E191</f>
-        <v>44.1210191462479</v>
+        <v>44.121019146248</v>
       </c>
       <c r="F192" s="21" t="n">
         <f aca="false">F190/F191</f>
@@ -51179,7 +51179,7 @@
       </c>
       <c r="G192" s="21" t="n">
         <f aca="false">G190/G191</f>
-        <v>56.3165986324204</v>
+        <v>56.3165986324205</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51195,7 +51195,7 @@
       </c>
       <c r="E193" s="15" t="n">
         <f aca="false">E192/D192-1</f>
-        <v>0.53611521481951</v>
+        <v>0.536115214819512</v>
       </c>
       <c r="F193" s="15" t="n">
         <f aca="false">F192/E192-1</f>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="G193" s="15" t="n">
         <f aca="false">G192/F192-1</f>
-        <v>0.0732440355940052</v>
+        <v>0.0732440355940047</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51251,7 +51251,7 @@
       </c>
       <c r="D199" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E199" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51350,7 +51350,7 @@
       </c>
       <c r="D203" s="19" t="n">
         <f aca="false">D201*D202</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E203" s="19" t="n">
         <f aca="false">E201*E202</f>
@@ -51374,7 +51374,7 @@
       </c>
       <c r="D204" s="19" t="n">
         <f aca="false">D203*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E204" s="19" t="n">
         <f aca="false">E203*fx</f>
@@ -51449,7 +51449,7 @@
       </c>
       <c r="G207" s="15" t="n">
         <f aca="false">$D$205*G206</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51473,7 +51473,7 @@
       </c>
       <c r="G208" s="19" t="n">
         <f aca="false">G204*G207</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51524,11 +51524,11 @@
       </c>
       <c r="F210" s="19" t="n">
         <f aca="false">F208*(1-F209)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G210" s="19" t="n">
         <f aca="false">G208*(1-G209)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51585,7 +51585,7 @@
       </c>
       <c r="F213" s="19" t="n">
         <f aca="false">F210+F212</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G213" s="19" t="n">
         <f aca="false">G210+G212</f>
@@ -51605,11 +51605,11 @@
       </c>
       <c r="E214" s="15" t="n">
         <f aca="false">E213/D213-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F214" s="15" t="n">
         <f aca="false">F213/E213-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G214" s="15" t="n">
         <f aca="false">G213/F213-1</f>
@@ -51637,11 +51637,11 @@
       </c>
       <c r="F215" s="15" t="n">
         <f aca="false">F210/F213</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G215" s="15" t="n">
         <f aca="false">G210/G213</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51653,7 +51653,7 @@
       </c>
       <c r="D216" s="16" t="n">
         <f aca="false">D210/fx/D201</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E216" s="16" t="n">
         <f aca="false">E210/fx/E201</f>
@@ -51685,7 +51685,7 @@
       </c>
       <c r="F217" s="19" t="n">
         <f aca="false">F208/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G217" s="19" t="n">
         <f aca="false">G208/fx/odm_vr</f>
@@ -51842,7 +51842,7 @@
       </c>
       <c r="E224" s="19" t="n">
         <f aca="false">D224*(1+MAX(0,phi*E214))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F224" s="19" t="n">
         <f aca="false">E224*(1+MAX(0,phi*F214))</f>
@@ -51850,7 +51850,7 @@
       </c>
       <c r="G224" s="19" t="n">
         <f aca="false">F224*(1+MAX(0,phi*G214))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51870,7 +51870,7 @@
       </c>
       <c r="E225" s="19" t="n">
         <f aca="false">E224+0*E213</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F225" s="19" t="n">
         <f aca="false">F224+0*F213</f>
@@ -51878,7 +51878,7 @@
       </c>
       <c r="G225" s="19" t="n">
         <f aca="false">G224+0*G213</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51898,7 +51898,7 @@
       </c>
       <c r="E226" s="19" t="n">
         <f aca="false">E221-E225</f>
-        <v>190.416391931755</v>
+        <v>190.416391931756</v>
       </c>
       <c r="F226" s="19" t="n">
         <f aca="false">F221-F225</f>
@@ -51982,11 +51982,11 @@
       </c>
       <c r="E229" s="19" t="n">
         <f aca="false">E226*E228</f>
-        <v>164.710179020968</v>
+        <v>164.710179020969</v>
       </c>
       <c r="F229" s="19" t="n">
         <f aca="false">F226*F228</f>
-        <v>191.967175122873</v>
+        <v>191.967175122874</v>
       </c>
       <c r="G229" s="19" t="n">
         <f aca="false">G226*G228</f>
@@ -52042,7 +52042,7 @@
       </c>
       <c r="F231" s="21" t="n">
         <f aca="false">F229/F230</f>
-        <v>49.8020781368128</v>
+        <v>49.8020781368129</v>
       </c>
       <c r="G231" s="21" t="n">
         <f aca="false">G229/G230</f>
@@ -52062,15 +52062,15 @@
       </c>
       <c r="E232" s="15" t="n">
         <f aca="false">E231/D231-1</f>
-        <v>0.487713094538683</v>
+        <v>0.487713094538685</v>
       </c>
       <c r="F232" s="15" t="n">
         <f aca="false">F231/E231-1</f>
-        <v>0.165484587922371</v>
+        <v>0.165484587922372</v>
       </c>
       <c r="G232" s="15" t="n">
         <f aca="false">G231/F231-1</f>
-        <v>0.0676458949056507</v>
+        <v>0.0676458949056502</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52118,7 +52118,7 @@
       </c>
       <c r="D238" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E238" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -52217,7 +52217,7 @@
       </c>
       <c r="D242" s="19" t="n">
         <f aca="false">D240*D241</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E242" s="19" t="n">
         <f aca="false">E240*E241</f>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="D243" s="19" t="n">
         <f aca="false">D242*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E243" s="19" t="n">
         <f aca="false">E242*fx</f>
@@ -52316,7 +52316,7 @@
       </c>
       <c r="G246" s="15" t="n">
         <f aca="false">$D$244*G245</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52340,7 +52340,7 @@
       </c>
       <c r="G247" s="19" t="n">
         <f aca="false">G243*G246</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52391,11 +52391,11 @@
       </c>
       <c r="F249" s="19" t="n">
         <f aca="false">F247*(1-F248)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G249" s="19" t="n">
         <f aca="false">G247*(1-G248)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52452,7 +52452,7 @@
       </c>
       <c r="F252" s="19" t="n">
         <f aca="false">F249+F251</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G252" s="19" t="n">
         <f aca="false">G249+G251</f>
@@ -52472,11 +52472,11 @@
       </c>
       <c r="E253" s="15" t="n">
         <f aca="false">E252/D252-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F253" s="15" t="n">
         <f aca="false">F252/E252-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G253" s="15" t="n">
         <f aca="false">G252/F252-1</f>
@@ -52504,11 +52504,11 @@
       </c>
       <c r="F254" s="15" t="n">
         <f aca="false">F249/F252</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G254" s="15" t="n">
         <f aca="false">G249/G252</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52520,7 +52520,7 @@
       </c>
       <c r="D255" s="16" t="n">
         <f aca="false">D249/fx/D240</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E255" s="16" t="n">
         <f aca="false">E249/fx/E240</f>
@@ -52552,7 +52552,7 @@
       </c>
       <c r="F256" s="19" t="n">
         <f aca="false">F247/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G256" s="19" t="n">
         <f aca="false">G247/fx/odm_vr</f>
@@ -52595,7 +52595,7 @@
       </c>
       <c r="E259" s="21" t="n">
         <f aca="false">($D$258+d_ai+vrd)*E247*(1-E248*(1-keep_hi))</f>
-        <v>196.349723440207</v>
+        <v>196.349723440208</v>
       </c>
       <c r="F259" s="21" t="n">
         <f aca="false">($D$258+d_ai+vrd)*F247*(1-F248*(1-keep_hi))</f>
@@ -52626,7 +52626,7 @@
       </c>
       <c r="E260" s="19" t="n">
         <f aca="false">$D$258*E251+E259</f>
-        <v>279.686326006607</v>
+        <v>279.686326006608</v>
       </c>
       <c r="F260" s="19" t="n">
         <f aca="false">$D$258*F251+F259</f>
@@ -52658,7 +52658,7 @@
       </c>
       <c r="F261" s="11" t="n">
         <f aca="false">F260/F252</f>
-        <v>0.0531660277163988</v>
+        <v>0.0531660277163987</v>
       </c>
       <c r="G261" s="11" t="n">
         <f aca="false">G260/G252</f>
@@ -52709,7 +52709,7 @@
       </c>
       <c r="E263" s="19" t="n">
         <f aca="false">D263*(1+MAX(0,phi*E253))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F263" s="19" t="n">
         <f aca="false">E263*(1+MAX(0,phi*F253))</f>
@@ -52717,7 +52717,7 @@
       </c>
       <c r="G263" s="19" t="n">
         <f aca="false">F263*(1+MAX(0,phi*G253))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52737,7 +52737,7 @@
       </c>
       <c r="E264" s="19" t="n">
         <f aca="false">E263+0*E252</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F264" s="19" t="n">
         <f aca="false">F263+0*F252</f>
@@ -52745,7 +52745,7 @@
       </c>
       <c r="G264" s="19" t="n">
         <f aca="false">G263+0*G252</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52769,11 +52769,11 @@
       </c>
       <c r="F265" s="19" t="n">
         <f aca="false">F260-F264</f>
-        <v>236.114453453139</v>
+        <v>236.11445345314</v>
       </c>
       <c r="G265" s="19" t="n">
         <f aca="false">G260-G264</f>
-        <v>256.078263818143</v>
+        <v>256.078263818144</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52801,7 +52801,7 @@
       </c>
       <c r="G266" s="11" t="n">
         <f aca="false">G265/G252</f>
-        <v>0.0417855843229528</v>
+        <v>0.0417855843229527</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52905,7 +52905,7 @@
       </c>
       <c r="E270" s="21" t="n">
         <f aca="false">E268/E269</f>
-        <v>44.052659002228</v>
+        <v>44.0526590022281</v>
       </c>
       <c r="F270" s="21" t="n">
         <f aca="false">F268/F269</f>
@@ -52913,7 +52913,7 @@
       </c>
       <c r="G270" s="21" t="n">
         <f aca="false">G268/G269</f>
-        <v>57.4657812552334</v>
+        <v>57.4657812552335</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="E271" s="15" t="n">
         <f aca="false">E270/D270-1</f>
-        <v>0.533735191435006</v>
+        <v>0.533735191435008</v>
       </c>
       <c r="F271" s="15" t="n">
         <f aca="false">F270/E270-1</f>
@@ -52937,7 +52937,7 @@
       </c>
       <c r="G271" s="15" t="n">
         <f aca="false">G270/F270-1</f>
-        <v>0.084551411711719</v>
+        <v>0.0845514117117188</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52985,7 +52985,7 @@
       </c>
       <c r="D277" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E277" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -53084,7 +53084,7 @@
       </c>
       <c r="D281" s="19" t="n">
         <f aca="false">D279*D280</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E281" s="19" t="n">
         <f aca="false">E279*E280</f>
@@ -53108,7 +53108,7 @@
       </c>
       <c r="D282" s="19" t="n">
         <f aca="false">D281*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E282" s="19" t="n">
         <f aca="false">E281*fx</f>
@@ -53183,7 +53183,7 @@
       </c>
       <c r="G285" s="15" t="n">
         <f aca="false">$D$283*G284</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53203,11 +53203,11 @@
       </c>
       <c r="F286" s="19" t="n">
         <f aca="false">F282*F285</f>
-        <v>4995.77621824561</v>
+        <v>4995.77621824562</v>
       </c>
       <c r="G286" s="19" t="n">
         <f aca="false">G282*G285</f>
-        <v>5391.45372814681</v>
+        <v>5391.45372814682</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53339,11 +53339,11 @@
       </c>
       <c r="E292" s="15" t="n">
         <f aca="false">E291/D291-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F292" s="15" t="n">
         <f aca="false">F291/E291-1</f>
-        <v>-0.0647143710072587</v>
+        <v>-0.0647143710072586</v>
       </c>
       <c r="G292" s="15" t="n">
         <f aca="false">G291/F291-1</f>
@@ -53387,7 +53387,7 @@
       </c>
       <c r="D294" s="16" t="n">
         <f aca="false">D288/fx/D279</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E294" s="16" t="n">
         <f aca="false">E288/fx/E279</f>
@@ -53395,7 +53395,7 @@
       </c>
       <c r="F294" s="16" t="n">
         <f aca="false">F288/fx/F279</f>
-        <v>2.36577660491208</v>
+        <v>2.36577660491209</v>
       </c>
       <c r="G294" s="16" t="n">
         <f aca="false">G288/fx/G279</f>
@@ -53419,7 +53419,7 @@
       </c>
       <c r="F295" s="19" t="n">
         <f aca="false">F286/fx/odm_vr</f>
-        <v>23.1285936029889</v>
+        <v>23.128593602989</v>
       </c>
       <c r="G295" s="19" t="n">
         <f aca="false">G286/fx/odm_vr</f>
@@ -53462,7 +53462,7 @@
       </c>
       <c r="E298" s="21" t="n">
         <f aca="false">($D$297+d_ai+vrd)*E286*(1-E287*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F298" s="21" t="n">
         <f aca="false">($D$297+d_ai+vrd)*F286*(1-F287*(1-keep))</f>
@@ -53470,7 +53470,7 @@
       </c>
       <c r="G298" s="21" t="n">
         <f aca="false">($D$297+d_ai+vrd)*G286*(1-G287*(1-keep))</f>
-        <v>211.479520894418</v>
+        <v>211.479520894419</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>423</v>
@@ -53493,7 +53493,7 @@
       </c>
       <c r="E299" s="19" t="n">
         <f aca="false">$D$297*E290+E298</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F299" s="19" t="n">
         <f aca="false">$D$297*F290+F298</f>
@@ -53576,15 +53576,15 @@
       </c>
       <c r="E302" s="19" t="n">
         <f aca="false">D302*(1+MAX(0,phi*E292))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F302" s="19" t="n">
         <f aca="false">E302*(1+MAX(0,phi*F292))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G302" s="19" t="n">
         <f aca="false">F302*(1+MAX(0,phi*G292))</f>
-        <v>83.8406387889182</v>
+        <v>83.8406387889183</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53604,15 +53604,15 @@
       </c>
       <c r="E303" s="19" t="n">
         <f aca="false">E302+0*E291</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F303" s="19" t="n">
         <f aca="false">F302+0*F291</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="G303" s="19" t="n">
         <f aca="false">G302+0*G291</f>
-        <v>83.8406387889182</v>
+        <v>83.8406387889183</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53668,7 +53668,7 @@
       </c>
       <c r="G305" s="11" t="n">
         <f aca="false">G304/G291</f>
-        <v>0.0395844294252083</v>
+        <v>0.0395844294252084</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53772,15 +53772,15 @@
       </c>
       <c r="E309" s="21" t="n">
         <f aca="false">E307/E308</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F309" s="21" t="n">
         <f aca="false">F307/F308</f>
-        <v>44.5645352051176</v>
+        <v>44.5645352051177</v>
       </c>
       <c r="G309" s="21" t="n">
         <f aca="false">G307/G308</f>
-        <v>48.0999308135516</v>
+        <v>48.0999308135517</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53796,7 +53796,7 @@
       </c>
       <c r="E310" s="15" t="n">
         <f aca="false">E309/D309-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F310" s="15" t="n">
         <f aca="false">F309/E309-1</f>
@@ -53804,7 +53804,7 @@
       </c>
       <c r="G310" s="15" t="n">
         <f aca="false">G309/F309-1</f>
-        <v>0.0793320426693918</v>
+        <v>0.079332042669392</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53852,7 +53852,7 @@
       </c>
       <c r="D316" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E316" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -53951,7 +53951,7 @@
       </c>
       <c r="D320" s="19" t="n">
         <f aca="false">D318*D319</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E320" s="19" t="n">
         <f aca="false">E318*E319</f>
@@ -53975,7 +53975,7 @@
       </c>
       <c r="D321" s="19" t="n">
         <f aca="false">D320*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E321" s="19" t="n">
         <f aca="false">E320*fx</f>
@@ -54050,7 +54050,7 @@
       </c>
       <c r="G324" s="15" t="n">
         <f aca="false">$D$322*G323</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54070,11 +54070,11 @@
       </c>
       <c r="F325" s="19" t="n">
         <f aca="false">F321*F324</f>
-        <v>7052.86054340557</v>
+        <v>7052.86054340558</v>
       </c>
       <c r="G325" s="19" t="n">
         <f aca="false">G321*G324</f>
-        <v>7611.4640867955</v>
+        <v>7611.46408679551</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54125,11 +54125,11 @@
       </c>
       <c r="F327" s="19" t="n">
         <f aca="false">F325*(1-F326)</f>
-        <v>5642.28843472445</v>
+        <v>5642.28843472446</v>
       </c>
       <c r="G327" s="19" t="n">
         <f aca="false">G325*(1-G326)</f>
-        <v>5708.59806509662</v>
+        <v>5708.59806509663</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54186,11 +54186,11 @@
       </c>
       <c r="F330" s="19" t="n">
         <f aca="false">F327+F329</f>
-        <v>6986.62442800445</v>
+        <v>6986.62442800446</v>
       </c>
       <c r="G330" s="19" t="n">
         <f aca="false">G327+G329</f>
-        <v>7079.82077824222</v>
+        <v>7079.82077824223</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54206,15 +54206,15 @@
       </c>
       <c r="E331" s="15" t="n">
         <f aca="false">E330/D330-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F331" s="15" t="n">
         <f aca="false">F330/E330-1</f>
-        <v>0.223467903221142</v>
+        <v>0.223467903221143</v>
       </c>
       <c r="G331" s="15" t="n">
         <f aca="false">G330/F330-1</f>
-        <v>0.0133392529107776</v>
+        <v>0.0133392529107774</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54238,11 +54238,11 @@
       </c>
       <c r="F332" s="15" t="n">
         <f aca="false">F327/F330</f>
-        <v>0.807584333874953</v>
+        <v>0.807584333874954</v>
       </c>
       <c r="G332" s="15" t="n">
         <f aca="false">G327/G330</f>
-        <v>0.806319572755336</v>
+        <v>0.806319572755337</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="D333" s="16" t="n">
         <f aca="false">D327/fx/D318</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E333" s="16" t="n">
         <f aca="false">E327/fx/E318</f>
@@ -54262,7 +54262,7 @@
       </c>
       <c r="F333" s="16" t="n">
         <f aca="false">F327/fx/F318</f>
-        <v>3.33991991281706</v>
+        <v>3.33991991281707</v>
       </c>
       <c r="G333" s="16" t="n">
         <f aca="false">G327/fx/G318</f>
@@ -54286,7 +54286,7 @@
       </c>
       <c r="F334" s="19" t="n">
         <f aca="false">F325/fx/odm_vr</f>
-        <v>32.6521321453961</v>
+        <v>32.6521321453962</v>
       </c>
       <c r="G334" s="19" t="n">
         <f aca="false">G325/fx/odm_vr</f>
@@ -54329,7 +54329,7 @@
       </c>
       <c r="E337" s="21" t="n">
         <f aca="false">($D$336+d_ai+vrd)*E325*(1-E326*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F337" s="21" t="n">
         <f aca="false">($D$336+d_ai+vrd)*F325*(1-F326*(1-keep))</f>
@@ -54337,7 +54337,7 @@
       </c>
       <c r="G337" s="21" t="n">
         <f aca="false">($D$336+d_ai+vrd)*G325*(1-G326*(1-keep))</f>
-        <v>298.559323615649</v>
+        <v>298.55932361565</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>423</v>
@@ -54360,7 +54360,7 @@
       </c>
       <c r="E338" s="19" t="n">
         <f aca="false">$D$336*E329+E337</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F338" s="19" t="n">
         <f aca="false">$D$336*F329+F337</f>
@@ -54443,15 +54443,15 @@
       </c>
       <c r="E341" s="19" t="n">
         <f aca="false">D341*(1+MAX(0,phi*E331))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F341" s="19" t="n">
         <f aca="false">E341*(1+MAX(0,phi*F331))</f>
-        <v>90.8324940350617</v>
+        <v>90.8324940350618</v>
       </c>
       <c r="G341" s="19" t="n">
         <f aca="false">F341*(1+MAX(0,phi*G331))</f>
-        <v>91.3171490792419</v>
+        <v>91.317149079242</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54471,15 +54471,15 @@
       </c>
       <c r="E342" s="19" t="n">
         <f aca="false">E341+0*E330</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F342" s="19" t="n">
         <f aca="false">F341+0*F330</f>
-        <v>90.8324940350617</v>
+        <v>90.8324940350618</v>
       </c>
       <c r="G342" s="19" t="n">
         <f aca="false">G341+0*G330</f>
-        <v>91.3171490792419</v>
+        <v>91.317149079242</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="F343" s="19" t="n">
         <f aca="false">F338-F342</f>
-        <v>272.237674612964</v>
+        <v>272.237674612965</v>
       </c>
       <c r="G343" s="19" t="n">
         <f aca="false">G338-G342</f>
@@ -54639,7 +54639,7 @@
       </c>
       <c r="E348" s="21" t="n">
         <f aca="false">E346/E347</f>
-        <v>43.61203627664</v>
+        <v>43.6120362766401</v>
       </c>
       <c r="F348" s="21" t="n">
         <f aca="false">F346/F347</f>
@@ -54647,7 +54647,7 @@
       </c>
       <c r="G348" s="21" t="n">
         <f aca="false">G346/G347</f>
-        <v>65.9634750356395</v>
+        <v>65.9634750356396</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54663,7 +54663,7 @@
       </c>
       <c r="E349" s="15" t="n">
         <f aca="false">E348/D348-1</f>
-        <v>0.518394492469565</v>
+        <v>0.518394492469567</v>
       </c>
       <c r="F349" s="15" t="n">
         <f aca="false">F348/E348-1</f>
@@ -54671,7 +54671,7 @@
       </c>
       <c r="G349" s="15" t="n">
         <f aca="false">G348/F348-1</f>
-        <v>0.079738784370633</v>
+        <v>0.0797387843706332</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54719,7 +54719,7 @@
       </c>
       <c r="D355" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E355" s="21" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -54818,7 +54818,7 @@
       </c>
       <c r="D359" s="19" t="n">
         <f aca="false">D357*D358</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E359" s="19" t="n">
         <f aca="false">E357*E358</f>
@@ -54842,7 +54842,7 @@
       </c>
       <c r="D360" s="19" t="n">
         <f aca="false">D359*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E360" s="19" t="n">
         <f aca="false">E359*fx</f>
@@ -54917,7 +54917,7 @@
       </c>
       <c r="G363" s="15" t="n">
         <f aca="false">$D$361*G362</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54937,11 +54937,11 @@
       </c>
       <c r="F364" s="19" t="n">
         <f aca="false">F360*F363</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G364" s="19" t="n">
         <f aca="false">G360*G363</f>
-        <v>5074.309391197</v>
+        <v>5074.30939119701</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54988,7 +54988,7 @@
       </c>
       <c r="E366" s="19" t="n">
         <f aca="false">E364*(1-E365)</f>
-        <v>3514.02599966903</v>
+        <v>3514.02599966904</v>
       </c>
       <c r="F366" s="19" t="n">
         <f aca="false">F364*(1-F365)</f>
@@ -55049,7 +55049,7 @@
       </c>
       <c r="E369" s="19" t="n">
         <f aca="false">E366+E368</f>
-        <v>4832.00246366903</v>
+        <v>4832.00246366904</v>
       </c>
       <c r="F369" s="19" t="n">
         <f aca="false">F366+F368</f>
@@ -55073,11 +55073,11 @@
       </c>
       <c r="E370" s="15" t="n">
         <f aca="false">E369/D369-1</f>
-        <v>0.208388810822734</v>
+        <v>0.208388810822735</v>
       </c>
       <c r="F370" s="15" t="n">
         <f aca="false">F369/E369-1</f>
-        <v>0.0566761202668469</v>
+        <v>0.0566761202668467</v>
       </c>
       <c r="G370" s="15" t="n">
         <f aca="false">G369/F369-1</f>
@@ -55101,11 +55101,11 @@
       </c>
       <c r="E371" s="15" t="n">
         <f aca="false">E366/E369</f>
-        <v>0.727240109269473</v>
+        <v>0.727240109269474</v>
       </c>
       <c r="F371" s="15" t="n">
         <f aca="false">F366/F369</f>
-        <v>0.736707319102774</v>
+        <v>0.736707319102775</v>
       </c>
       <c r="G371" s="15" t="n">
         <f aca="false">G366/G369</f>
@@ -55121,11 +55121,11 @@
       </c>
       <c r="D372" s="16" t="n">
         <f aca="false">D366/fx/D357</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E372" s="16" t="n">
         <f aca="false">E366/fx/E357</f>
-        <v>3.29597359817473</v>
+        <v>3.29597359817474</v>
       </c>
       <c r="F372" s="16" t="n">
         <f aca="false">F366/fx/F357</f>
@@ -55149,7 +55149,7 @@
       </c>
       <c r="E373" s="19" t="n">
         <f aca="false">E364/fx/odm_vr</f>
-        <v>18.0762654303962</v>
+        <v>18.0762654303963</v>
       </c>
       <c r="F373" s="19" t="n">
         <f aca="false">F364/fx/odm_vr</f>
@@ -55196,7 +55196,7 @@
       </c>
       <c r="E376" s="21" t="n">
         <f aca="false">($D$375+d_ai+vrd)*E364*(1-E365*(1-keep))</f>
-        <v>155.508980964644</v>
+        <v>155.508980964645</v>
       </c>
       <c r="F376" s="21" t="n">
         <f aca="false">($D$375+d_ai+vrd)*F364*(1-F365*(1-keep))</f>
@@ -55227,7 +55227,7 @@
       </c>
       <c r="E377" s="19" t="n">
         <f aca="false">$D$375*E368+E376</f>
-        <v>238.845583531044</v>
+        <v>238.845583531045</v>
       </c>
       <c r="F377" s="19" t="n">
         <f aca="false">$D$375*F368+F376</f>
@@ -55514,7 +55514,7 @@
       </c>
       <c r="G387" s="21" t="n">
         <f aca="false">G385/G386</f>
-        <v>46.3247732119397</v>
+        <v>46.3247732119398</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55530,15 +55530,15 @@
       </c>
       <c r="E388" s="15" t="n">
         <f aca="false">E387/D387-1</f>
-        <v>0.263526777911564</v>
+        <v>0.263526777911566</v>
       </c>
       <c r="F388" s="15" t="n">
         <f aca="false">F387/E387-1</f>
-        <v>0.184187584830392</v>
+        <v>0.184187584830393</v>
       </c>
       <c r="G388" s="15" t="n">
         <f aca="false">G387/F387-1</f>
-        <v>0.0779201813708916</v>
+        <v>0.077920181370891</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55586,7 +55586,7 @@
       </c>
       <c r="D394" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E394" s="21" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -55685,7 +55685,7 @@
       </c>
       <c r="D398" s="19" t="n">
         <f aca="false">D396*D397</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E398" s="19" t="n">
         <f aca="false">E396*E397</f>
@@ -55709,7 +55709,7 @@
       </c>
       <c r="D399" s="19" t="n">
         <f aca="false">D398*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E399" s="19" t="n">
         <f aca="false">E398*fx</f>
@@ -55784,7 +55784,7 @@
       </c>
       <c r="G402" s="15" t="n">
         <f aca="false">$D$400*G401</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55800,15 +55800,15 @@
       </c>
       <c r="E403" s="19" t="n">
         <f aca="false">E399*E402</f>
-        <v>5856.70999944838</v>
+        <v>5856.70999944839</v>
       </c>
       <c r="F403" s="19" t="n">
         <f aca="false">F399*F402</f>
-        <v>7052.86054340557</v>
+        <v>7052.86054340558</v>
       </c>
       <c r="G403" s="19" t="n">
         <f aca="false">G399*G402</f>
-        <v>7611.4640867955</v>
+        <v>7611.46408679551</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55859,11 +55859,11 @@
       </c>
       <c r="F405" s="19" t="n">
         <f aca="false">F403*(1-F404)</f>
-        <v>5642.28843472445</v>
+        <v>5642.28843472446</v>
       </c>
       <c r="G405" s="19" t="n">
         <f aca="false">G403*(1-G404)</f>
-        <v>5708.59806509662</v>
+        <v>5708.59806509663</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55920,11 +55920,11 @@
       </c>
       <c r="F408" s="19" t="n">
         <f aca="false">F405+F407</f>
-        <v>6986.62442800445</v>
+        <v>6986.62442800446</v>
       </c>
       <c r="G408" s="19" t="n">
         <f aca="false">G405+G407</f>
-        <v>7079.82077824222</v>
+        <v>7079.82077824223</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55940,7 +55940,7 @@
       </c>
       <c r="E409" s="15" t="n">
         <f aca="false">E408/D408-1</f>
-        <v>0.647783216234102</v>
+        <v>0.647783216234103</v>
       </c>
       <c r="F409" s="15" t="n">
         <f aca="false">F408/E408-1</f>
@@ -55972,11 +55972,11 @@
       </c>
       <c r="F410" s="15" t="n">
         <f aca="false">F405/F408</f>
-        <v>0.807584333874953</v>
+        <v>0.807584333874954</v>
       </c>
       <c r="G410" s="15" t="n">
         <f aca="false">G405/G408</f>
-        <v>0.806319572755336</v>
+        <v>0.806319572755337</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55988,7 +55988,7 @@
       </c>
       <c r="D411" s="16" t="n">
         <f aca="false">D405/fx/D396</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E411" s="16" t="n">
         <f aca="false">E405/fx/E396</f>
@@ -56020,7 +56020,7 @@
       </c>
       <c r="F412" s="19" t="n">
         <f aca="false">F403/fx/odm_vr</f>
-        <v>32.6521321453961</v>
+        <v>32.6521321453962</v>
       </c>
       <c r="G412" s="19" t="n">
         <f aca="false">G403/fx/odm_vr</f>
@@ -56063,7 +56063,7 @@
       </c>
       <c r="E415" s="21" t="n">
         <f aca="false">($D$414+d_ai+vrd)*E403*(1-E404*(1-keep))</f>
-        <v>233.263471446966</v>
+        <v>233.263471446967</v>
       </c>
       <c r="F415" s="21" t="n">
         <f aca="false">($D$414+d_ai+vrd)*F403*(1-F404*(1-keep))</f>
@@ -56071,7 +56071,7 @@
       </c>
       <c r="G415" s="21" t="n">
         <f aca="false">($D$414+d_ai+vrd)*G403*(1-G404*(1-keep))</f>
-        <v>298.559323615649</v>
+        <v>298.55932361565</v>
       </c>
       <c r="H415" s="4" t="s">
         <v>423</v>
@@ -56094,7 +56094,7 @@
       </c>
       <c r="E416" s="19" t="n">
         <f aca="false">$D$414*E407+E415</f>
-        <v>316.600074013366</v>
+        <v>316.600074013367</v>
       </c>
       <c r="F416" s="19" t="n">
         <f aca="false">$D$414*F407+F415</f>
@@ -56177,15 +56177,15 @@
       </c>
       <c r="E419" s="19" t="n">
         <f aca="false">D419*(1+MAX(0,phi*E409))</f>
-        <v>89.635484771895</v>
+        <v>89.6354847718951</v>
       </c>
       <c r="F419" s="19" t="n">
         <f aca="false">E419*(1+MAX(0,phi*F409))</f>
-        <v>91.799077950882</v>
+        <v>91.7990779508821</v>
       </c>
       <c r="G419" s="19" t="n">
         <f aca="false">F419*(1+MAX(0,phi*G409))</f>
-        <v>92.2888903979872</v>
+        <v>92.2888903979873</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56205,15 +56205,15 @@
       </c>
       <c r="E420" s="19" t="n">
         <f aca="false">E419+0*E408</f>
-        <v>89.635484771895</v>
+        <v>89.6354847718951</v>
       </c>
       <c r="F420" s="19" t="n">
         <f aca="false">F419+0*F408</f>
-        <v>91.799077950882</v>
+        <v>91.7990779508821</v>
       </c>
       <c r="G420" s="19" t="n">
         <f aca="false">G419+0*G408</f>
-        <v>92.2888903979872</v>
+        <v>92.2888903979873</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56233,7 +56233,7 @@
       </c>
       <c r="E421" s="19" t="n">
         <f aca="false">E416-E420</f>
-        <v>226.964589241471</v>
+        <v>226.964589241472</v>
       </c>
       <c r="F421" s="19" t="n">
         <f aca="false">F416-F420</f>
@@ -56373,15 +56373,15 @@
       </c>
       <c r="E426" s="21" t="n">
         <f aca="false">E424/E425</f>
-        <v>50.9324658936953</v>
+        <v>50.9324658936954</v>
       </c>
       <c r="F426" s="21" t="n">
         <f aca="false">F424/F425</f>
-        <v>60.8751595174091</v>
+        <v>60.8751595174092</v>
       </c>
       <c r="G426" s="21" t="n">
         <f aca="false">G424/G425</f>
-        <v>65.7454093816981</v>
+        <v>65.7454093816982</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56397,15 +56397,15 @@
       </c>
       <c r="E427" s="15" t="n">
         <f aca="false">E426/D426-1</f>
-        <v>0.773262207027567</v>
+        <v>0.773262207027569</v>
       </c>
       <c r="F427" s="15" t="n">
         <f aca="false">F426/E426-1</f>
-        <v>0.195213277999653</v>
+        <v>0.195213277999654</v>
       </c>
       <c r="G427" s="15" t="n">
         <f aca="false">G426/F426-1</f>
-        <v>0.0800038949039001</v>
+        <v>0.0800038949038999</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56453,7 +56453,7 @@
       </c>
       <c r="D433" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E433" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56552,7 +56552,7 @@
       </c>
       <c r="D437" s="19" t="n">
         <f aca="false">D435*D436</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E437" s="19" t="n">
         <f aca="false">E435*E436</f>
@@ -56576,7 +56576,7 @@
       </c>
       <c r="D438" s="19" t="n">
         <f aca="false">D437*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E438" s="19" t="n">
         <f aca="false">E437*fx</f>
@@ -56651,7 +56651,7 @@
       </c>
       <c r="G441" s="15" t="n">
         <f aca="false">$D$439*G440</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56675,7 +56675,7 @@
       </c>
       <c r="G442" s="19" t="n">
         <f aca="false">G438*G441</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56726,11 +56726,11 @@
       </c>
       <c r="F444" s="19" t="n">
         <f aca="false">F442*(1-F443)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G444" s="19" t="n">
         <f aca="false">G442*(1-G443)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56787,11 +56787,11 @@
       </c>
       <c r="F447" s="19" t="n">
         <f aca="false">F444+F446</f>
-        <v>5856.73592093704</v>
+        <v>5856.73592093705</v>
       </c>
       <c r="G447" s="19" t="n">
         <f aca="false">G444+G446</f>
-        <v>5854.25250164718</v>
+        <v>5854.25250164719</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56807,11 +56807,11 @@
       </c>
       <c r="E448" s="15" t="n">
         <f aca="false">E447/D447-1</f>
-        <v>0.402486013528418</v>
+        <v>0.402486013528419</v>
       </c>
       <c r="F448" s="15" t="n">
         <f aca="false">F447/E447-1</f>
-        <v>0.0443273489820557</v>
+        <v>0.0443273489820559</v>
       </c>
       <c r="G448" s="15" t="n">
         <f aca="false">G447/F447-1</f>
@@ -56835,11 +56835,11 @@
       </c>
       <c r="E449" s="15" t="n">
         <f aca="false">E444/E447</f>
-        <v>0.78324204514868</v>
+        <v>0.783242045148681</v>
       </c>
       <c r="F449" s="15" t="n">
         <f aca="false">F444/F447</f>
-        <v>0.802820392179261</v>
+        <v>0.802820392179262</v>
       </c>
       <c r="G449" s="15" t="n">
         <f aca="false">G444/G447</f>
@@ -56855,7 +56855,7 @@
       </c>
       <c r="D450" s="16" t="n">
         <f aca="false">D444/fx/D435</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E450" s="16" t="n">
         <f aca="false">E444/fx/E435</f>
@@ -56887,7 +56887,7 @@
       </c>
       <c r="F451" s="19" t="n">
         <f aca="false">F442/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G451" s="19" t="n">
         <f aca="false">G442/fx/odm_vr</f>
@@ -56930,7 +56930,7 @@
       </c>
       <c r="E454" s="21" t="n">
         <f aca="false">($D$453+d_ai+vrd)*E442*(1-E443*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F454" s="21" t="n">
         <f aca="false">($D$453+d_ai+vrd)*F442*(1-F443*(1-keep))</f>
@@ -56938,7 +56938,7 @@
       </c>
       <c r="G454" s="21" t="n">
         <f aca="false">($D$453+d_ai+vrd)*G442*(1-G443*(1-keep))</f>
-        <v>248.799436346374</v>
+        <v>248.799436346375</v>
       </c>
       <c r="H454" s="4" t="s">
         <v>423</v>
@@ -56961,7 +56961,7 @@
       </c>
       <c r="E455" s="19" t="n">
         <f aca="false">$D$453*E446+E454</f>
-        <v>271.250082941805</v>
+        <v>271.250082941806</v>
       </c>
       <c r="F455" s="19" t="n">
         <f aca="false">$D$453*F446+F454</f>
@@ -56969,7 +56969,7 @@
       </c>
       <c r="G455" s="19" t="n">
         <f aca="false">$D$453*G446+G454</f>
-        <v>318.169067050614</v>
+        <v>318.169067050615</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57044,7 +57044,7 @@
       </c>
       <c r="E458" s="19" t="n">
         <f aca="false">D458*(1+MAX(0,phi*E448))</f>
-        <v>82.6504631972458</v>
+        <v>82.6504631972459</v>
       </c>
       <c r="F458" s="19" t="n">
         <f aca="false">E458*(1+MAX(0,phi*F448))</f>
@@ -57072,7 +57072,7 @@
       </c>
       <c r="E459" s="19" t="n">
         <f aca="false">E458+0*E447</f>
-        <v>82.6504631972458</v>
+        <v>82.6504631972459</v>
       </c>
       <c r="F459" s="19" t="n">
         <f aca="false">F458+0*F447</f>
@@ -57108,7 +57108,7 @@
       </c>
       <c r="G460" s="19" t="n">
         <f aca="false">G455-G459</f>
-        <v>234.053133483099</v>
+        <v>234.0531334831</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57240,15 +57240,15 @@
       </c>
       <c r="E465" s="21" t="n">
         <f aca="false">E463/E464</f>
-        <v>42.3230942426171</v>
+        <v>42.3230942426172</v>
       </c>
       <c r="F465" s="21" t="n">
         <f aca="false">F463/F464</f>
-        <v>49.5102865044814</v>
+        <v>49.5102865044815</v>
       </c>
       <c r="G465" s="21" t="n">
         <f aca="false">G463/G464</f>
-        <v>52.5231855695235</v>
+        <v>52.5231855695236</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57264,7 +57264,7 @@
       </c>
       <c r="E466" s="15" t="n">
         <f aca="false">E465/D465-1</f>
-        <v>0.473518750526254</v>
+        <v>0.473518750526256</v>
       </c>
       <c r="F466" s="15" t="n">
         <f aca="false">F465/E465-1</f>
@@ -57272,7 +57272,7 @@
       </c>
       <c r="G466" s="15" t="n">
         <f aca="false">G465/F465-1</f>
-        <v>0.0608540018197914</v>
+        <v>0.0608540018197912</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57320,7 +57320,7 @@
       </c>
       <c r="D472" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E472" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57419,7 +57419,7 @@
       </c>
       <c r="D476" s="19" t="n">
         <f aca="false">D474*D475</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E476" s="19" t="n">
         <f aca="false">E474*E475</f>
@@ -57443,7 +57443,7 @@
       </c>
       <c r="D477" s="19" t="n">
         <f aca="false">D476*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E477" s="19" t="n">
         <f aca="false">E476*fx</f>
@@ -57518,7 +57518,7 @@
       </c>
       <c r="G480" s="15" t="n">
         <f aca="false">$D$478*G479</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57542,7 +57542,7 @@
       </c>
       <c r="G481" s="19" t="n">
         <f aca="false">G477*G480</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57593,11 +57593,11 @@
       </c>
       <c r="F483" s="19" t="n">
         <f aca="false">F481*(1-F482)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G483" s="19" t="n">
         <f aca="false">G481*(1-G482)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57654,11 +57654,11 @@
       </c>
       <c r="F486" s="19" t="n">
         <f aca="false">F483+F485</f>
-        <v>6166.78028717704</v>
+        <v>6166.78028717705</v>
       </c>
       <c r="G486" s="19" t="n">
         <f aca="false">G483+G485</f>
-        <v>6309.93070798158</v>
+        <v>6309.93070798159</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57674,7 +57674,7 @@
       </c>
       <c r="E487" s="15" t="n">
         <f aca="false">E486/D486-1</f>
-        <v>0.444086013528418</v>
+        <v>0.444086013528419</v>
       </c>
       <c r="F487" s="15" t="n">
         <f aca="false">F486/E486-1</f>
@@ -57702,7 +57702,7 @@
       </c>
       <c r="E488" s="15" t="n">
         <f aca="false">E483/E486</f>
-        <v>0.760679075371988</v>
+        <v>0.760679075371989</v>
       </c>
       <c r="F488" s="15" t="n">
         <f aca="false">F483/F486</f>
@@ -57722,7 +57722,7 @@
       </c>
       <c r="D489" s="16" t="n">
         <f aca="false">D483/fx/D474</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E489" s="16" t="n">
         <f aca="false">E483/fx/E474</f>
@@ -57754,7 +57754,7 @@
       </c>
       <c r="F490" s="19" t="n">
         <f aca="false">F481/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G490" s="19" t="n">
         <f aca="false">G481/fx/odm_vr</f>
@@ -57797,7 +57797,7 @@
       </c>
       <c r="E493" s="21" t="n">
         <f aca="false">($D$492+d_ai+vrd)*E481*(1-E482*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F493" s="21" t="n">
         <f aca="false">($D$492+d_ai+vrd)*F481*(1-F482*(1-keep))</f>
@@ -57805,7 +57805,7 @@
       </c>
       <c r="G493" s="21" t="n">
         <f aca="false">($D$492+d_ai+vrd)*G481*(1-G482*(1-keep))</f>
-        <v>248.799436346374</v>
+        <v>248.799436346375</v>
       </c>
       <c r="H493" s="4" t="s">
         <v>423</v>
@@ -57828,7 +57828,7 @@
       </c>
       <c r="E494" s="19" t="n">
         <f aca="false">$D$492*E485+E493</f>
-        <v>281.768294916205</v>
+        <v>281.768294916206</v>
       </c>
       <c r="F494" s="19" t="n">
         <f aca="false">$D$492*F485+F493</f>
@@ -57911,15 +57911,15 @@
       </c>
       <c r="E497" s="19" t="n">
         <f aca="false">D497*(1+MAX(0,phi*E487))</f>
-        <v>83.8350543556458</v>
+        <v>83.8350543556459</v>
       </c>
       <c r="F497" s="19" t="n">
         <f aca="false">E497*(1+MAX(0,phi*F487))</f>
-        <v>86.1131998179302</v>
+        <v>86.1131998179303</v>
       </c>
       <c r="G497" s="19" t="n">
         <f aca="false">F497*(1+MAX(0,phi*G487))</f>
-        <v>86.9127834072074</v>
+        <v>86.9127834072075</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57939,15 +57939,15 @@
       </c>
       <c r="E498" s="19" t="n">
         <f aca="false">E497+0*E486</f>
-        <v>83.8350543556458</v>
+        <v>83.8350543556459</v>
       </c>
       <c r="F498" s="19" t="n">
         <f aca="false">F497+0*F486</f>
-        <v>86.1131998179302</v>
+        <v>86.1131998179303</v>
       </c>
       <c r="G498" s="19" t="n">
         <f aca="false">G497+0*G486</f>
-        <v>86.9127834072074</v>
+        <v>86.9127834072075</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57975,7 +57975,7 @@
       </c>
       <c r="G499" s="19" t="n">
         <f aca="false">G494-G498</f>
-        <v>260.069145342172</v>
+        <v>260.069145342173</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58111,11 +58111,11 @@
       </c>
       <c r="F504" s="21" t="n">
         <f aca="false">F502/F503</f>
-        <v>53.4614364288283</v>
+        <v>53.4614364288284</v>
       </c>
       <c r="G504" s="21" t="n">
         <f aca="false">G502/G503</f>
-        <v>58.3613634153744</v>
+        <v>58.3613634153745</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58131,7 +58131,7 @@
       </c>
       <c r="E505" s="15" t="n">
         <f aca="false">E504/D504-1</f>
-        <v>0.546441831184135</v>
+        <v>0.546441831184136</v>
       </c>
       <c r="F505" s="15" t="n">
         <f aca="false">F504/E504-1</f>
@@ -58187,7 +58187,7 @@
       </c>
       <c r="D511" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E511" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58286,7 +58286,7 @@
       </c>
       <c r="D515" s="19" t="n">
         <f aca="false">D513*D514</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E515" s="19" t="n">
         <f aca="false">E513*E514</f>
@@ -58310,7 +58310,7 @@
       </c>
       <c r="D516" s="19" t="n">
         <f aca="false">D515*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E516" s="19" t="n">
         <f aca="false">E515*fx</f>
@@ -58385,7 +58385,7 @@
       </c>
       <c r="G519" s="15" t="n">
         <f aca="false">$D$517*G518</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58409,7 +58409,7 @@
       </c>
       <c r="G520" s="19" t="n">
         <f aca="false">G516*G519</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58460,11 +58460,11 @@
       </c>
       <c r="F522" s="19" t="n">
         <f aca="false">F520*(1-F521)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G522" s="19" t="n">
         <f aca="false">G520*(1-G521)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58521,7 +58521,7 @@
       </c>
       <c r="F525" s="19" t="n">
         <f aca="false">F522+F524</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G525" s="19" t="n">
         <f aca="false">G522+G524</f>
@@ -58541,11 +58541,11 @@
       </c>
       <c r="E526" s="15" t="n">
         <f aca="false">E525/D525-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F526" s="15" t="n">
         <f aca="false">F525/E525-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G526" s="15" t="n">
         <f aca="false">G525/F525-1</f>
@@ -58573,11 +58573,11 @@
       </c>
       <c r="F527" s="15" t="n">
         <f aca="false">F522/F525</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G527" s="15" t="n">
         <f aca="false">G522/G525</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58589,7 +58589,7 @@
       </c>
       <c r="D528" s="16" t="n">
         <f aca="false">D522/fx/D513</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E528" s="16" t="n">
         <f aca="false">E522/fx/E513</f>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="F529" s="19" t="n">
         <f aca="false">F520/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G529" s="19" t="n">
         <f aca="false">G520/fx/odm_vr</f>
@@ -58699,7 +58699,7 @@
       </c>
       <c r="F533" s="19" t="n">
         <f aca="false">$D$531*F524+F532</f>
-        <v>302.790710110949</v>
+        <v>302.79071011095</v>
       </c>
       <c r="G533" s="19" t="n">
         <f aca="false">$D$531*G524+G532</f>
@@ -58751,7 +58751,7 @@
       </c>
       <c r="F535" s="11" t="n">
         <f aca="false">F532/F522</f>
-        <v>0.0434026336773188</v>
+        <v>0.0434026336773189</v>
       </c>
       <c r="G535" s="11" t="n">
         <f aca="false">G532/G522</f>
@@ -58778,7 +58778,7 @@
       </c>
       <c r="E536" s="19" t="n">
         <f aca="false">D536*(1+MAX(0,phi*E526))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F536" s="19" t="n">
         <f aca="false">E536*(1+MAX(0,phi*F526))</f>
@@ -58786,7 +58786,7 @@
       </c>
       <c r="G536" s="19" t="n">
         <f aca="false">F536*(1+MAX(0,phi*G526))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58806,7 +58806,7 @@
       </c>
       <c r="E537" s="19" t="n">
         <f aca="false">E536+0*E525</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F537" s="19" t="n">
         <f aca="false">F536+0*F525</f>
@@ -58814,7 +58814,7 @@
       </c>
       <c r="G537" s="19" t="n">
         <f aca="false">G536+0*G525</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58918,7 +58918,7 @@
       </c>
       <c r="E541" s="19" t="n">
         <f aca="false">E538*E540</f>
-        <v>159.673961146245</v>
+        <v>159.673961146246</v>
       </c>
       <c r="F541" s="19" t="n">
         <f aca="false">F538*F540</f>
@@ -58998,15 +58998,15 @@
       </c>
       <c r="E544" s="15" t="n">
         <f aca="false">E543/D543-1</f>
-        <v>0.442224422717003</v>
+        <v>0.442224422717004</v>
       </c>
       <c r="F544" s="15" t="n">
         <f aca="false">F543/E543-1</f>
-        <v>0.177991882876812</v>
+        <v>0.177991882876813</v>
       </c>
       <c r="G544" s="15" t="n">
         <f aca="false">G543/F543-1</f>
-        <v>0.0761098179558255</v>
+        <v>0.0761098179558251</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59054,7 +59054,7 @@
       </c>
       <c r="D550" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E550" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59153,7 +59153,7 @@
       </c>
       <c r="D554" s="19" t="n">
         <f aca="false">D552*D553</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E554" s="19" t="n">
         <f aca="false">E552*E553</f>
@@ -59177,7 +59177,7 @@
       </c>
       <c r="D555" s="19" t="n">
         <f aca="false">D554*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E555" s="19" t="n">
         <f aca="false">E554*fx</f>
@@ -59252,7 +59252,7 @@
       </c>
       <c r="G558" s="15" t="n">
         <f aca="false">$D$556*G557</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59276,7 +59276,7 @@
       </c>
       <c r="G559" s="19" t="n">
         <f aca="false">G555*G558</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59327,11 +59327,11 @@
       </c>
       <c r="F561" s="19" t="n">
         <f aca="false">F559*(1-F560)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G561" s="19" t="n">
         <f aca="false">G559*(1-G560)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59388,7 +59388,7 @@
       </c>
       <c r="F564" s="19" t="n">
         <f aca="false">F561+F563</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G564" s="19" t="n">
         <f aca="false">G561+G563</f>
@@ -59408,11 +59408,11 @@
       </c>
       <c r="E565" s="15" t="n">
         <f aca="false">E564/D564-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F565" s="15" t="n">
         <f aca="false">F564/E564-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G565" s="15" t="n">
         <f aca="false">G564/F564-1</f>
@@ -59440,11 +59440,11 @@
       </c>
       <c r="F566" s="15" t="n">
         <f aca="false">F561/F564</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G566" s="15" t="n">
         <f aca="false">G561/G564</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="567" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59456,7 +59456,7 @@
       </c>
       <c r="D567" s="16" t="n">
         <f aca="false">D561/fx/D552</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E567" s="16" t="n">
         <f aca="false">E561/fx/E552</f>
@@ -59488,7 +59488,7 @@
       </c>
       <c r="F568" s="19" t="n">
         <f aca="false">F559/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G568" s="19" t="n">
         <f aca="false">G559/fx/odm_vr</f>
@@ -59570,7 +59570,7 @@
       </c>
       <c r="G572" s="19" t="n">
         <f aca="false">$D$570*G563+G571</f>
-        <v>351.201075920874</v>
+        <v>351.201075920875</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59645,7 +59645,7 @@
       </c>
       <c r="E575" s="19" t="n">
         <f aca="false">D575*(1+MAX(0,phi*E565))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F575" s="19" t="n">
         <f aca="false">E575*(1+MAX(0,phi*F565))</f>
@@ -59653,7 +59653,7 @@
       </c>
       <c r="G575" s="19" t="n">
         <f aca="false">F575*(1+MAX(0,phi*G565))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59673,7 +59673,7 @@
       </c>
       <c r="E576" s="19" t="n">
         <f aca="false">E575+0*E564</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F576" s="19" t="n">
         <f aca="false">F575+0*F564</f>
@@ -59681,7 +59681,7 @@
       </c>
       <c r="G576" s="19" t="n">
         <f aca="false">G575+0*G564</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59705,7 +59705,7 @@
       </c>
       <c r="F577" s="19" t="n">
         <f aca="false">F572-F576</f>
-        <v>245.320411862202</v>
+        <v>245.320411862203</v>
       </c>
       <c r="G577" s="19" t="n">
         <f aca="false">G572-G576</f>
@@ -59785,7 +59785,7 @@
       </c>
       <c r="E580" s="19" t="n">
         <f aca="false">E577*E579</f>
-        <v>176.540097326722</v>
+        <v>176.540097326723</v>
       </c>
       <c r="F580" s="19" t="n">
         <f aca="false">F577*F579</f>
@@ -59841,7 +59841,7 @@
       </c>
       <c r="E582" s="21" t="n">
         <f aca="false">E580/E581</f>
-        <v>45.7998286202753</v>
+        <v>45.7998286202754</v>
       </c>
       <c r="F582" s="21" t="n">
         <f aca="false">F580/F581</f>
@@ -59849,7 +59849,7 @@
       </c>
       <c r="G582" s="21" t="n">
         <f aca="false">G580/G581</f>
-        <v>59.5569784305317</v>
+        <v>59.5569784305318</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59865,7 +59865,7 @@
       </c>
       <c r="E583" s="15" t="n">
         <f aca="false">E582/D582-1</f>
-        <v>0.594564562222127</v>
+        <v>0.594564562222129</v>
       </c>
       <c r="F583" s="15" t="n">
         <f aca="false">F582/E582-1</f>
@@ -59873,7 +59873,7 @@
       </c>
       <c r="G583" s="15" t="n">
         <f aca="false">G582/F582-1</f>
-        <v>0.0818383490437205</v>
+        <v>0.0818383490437207</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59921,7 +59921,7 @@
       </c>
       <c r="D589" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E589" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60020,7 +60020,7 @@
       </c>
       <c r="D593" s="19" t="n">
         <f aca="false">D591*D592</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E593" s="19" t="n">
         <f aca="false">E591*E592</f>
@@ -60044,7 +60044,7 @@
       </c>
       <c r="D594" s="19" t="n">
         <f aca="false">D593*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E594" s="19" t="n">
         <f aca="false">E593*fx</f>
@@ -60119,7 +60119,7 @@
       </c>
       <c r="G597" s="15" t="n">
         <f aca="false">$D$595*G596</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60143,7 +60143,7 @@
       </c>
       <c r="G598" s="19" t="n">
         <f aca="false">G594*G597</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60194,11 +60194,11 @@
       </c>
       <c r="F600" s="19" t="n">
         <f aca="false">F598*(1-F599)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G600" s="19" t="n">
         <f aca="false">G598*(1-G599)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60255,7 +60255,7 @@
       </c>
       <c r="F603" s="19" t="n">
         <f aca="false">F600+F602</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G603" s="19" t="n">
         <f aca="false">G600+G602</f>
@@ -60275,11 +60275,11 @@
       </c>
       <c r="E604" s="15" t="n">
         <f aca="false">E603/D603-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F604" s="15" t="n">
         <f aca="false">F603/E603-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G604" s="15" t="n">
         <f aca="false">G603/F603-1</f>
@@ -60307,11 +60307,11 @@
       </c>
       <c r="F605" s="15" t="n">
         <f aca="false">F600/F603</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G605" s="15" t="n">
         <f aca="false">G600/G603</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60323,7 +60323,7 @@
       </c>
       <c r="D606" s="16" t="n">
         <f aca="false">D600/fx/D591</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E606" s="16" t="n">
         <f aca="false">E600/fx/E591</f>
@@ -60355,7 +60355,7 @@
       </c>
       <c r="F607" s="19" t="n">
         <f aca="false">F598/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G607" s="19" t="n">
         <f aca="false">G598/fx/odm_vr</f>
@@ -60402,11 +60402,11 @@
       </c>
       <c r="F610" s="21" t="n">
         <f aca="false">($D$609+d_ai+vrd_lo)*F598*(1-F599*(1-keep))</f>
-        <v>214.442853360571</v>
+        <v>214.442853360572</v>
       </c>
       <c r="G610" s="21" t="n">
         <f aca="false">($D$609+d_ai+vrd_lo)*G598*(1-G599*(1-keep))</f>
-        <v>230.24649263481</v>
+        <v>230.246492634811</v>
       </c>
       <c r="H610" s="4" t="s">
         <v>423</v>
@@ -60433,7 +60433,7 @@
       </c>
       <c r="F611" s="19" t="n">
         <f aca="false">$D$609*F602+F610</f>
-        <v>299.446187978299</v>
+        <v>299.4461879783</v>
       </c>
       <c r="G611" s="19" t="n">
         <f aca="false">$D$609*G602+G610</f>
@@ -60512,7 +60512,7 @@
       </c>
       <c r="E614" s="19" t="n">
         <f aca="false">D614*(1+MAX(0,phi*E604))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F614" s="19" t="n">
         <f aca="false">E614*(1+MAX(0,phi*F604))</f>
@@ -60520,7 +60520,7 @@
       </c>
       <c r="G614" s="19" t="n">
         <f aca="false">F614*(1+MAX(0,phi*G604))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60540,7 +60540,7 @@
       </c>
       <c r="E615" s="19" t="n">
         <f aca="false">E614+0*E603</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F615" s="19" t="n">
         <f aca="false">F614+0*F603</f>
@@ -60548,7 +60548,7 @@
       </c>
       <c r="G615" s="19" t="n">
         <f aca="false">G614+0*G603</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60708,11 +60708,11 @@
       </c>
       <c r="E621" s="21" t="n">
         <f aca="false">E619/E620</f>
-        <v>40.3591751534559</v>
+        <v>40.359175153456</v>
       </c>
       <c r="F621" s="21" t="n">
         <f aca="false">F619/F620</f>
-        <v>48.0468885855885</v>
+        <v>48.0468885855886</v>
       </c>
       <c r="G621" s="21" t="n">
         <f aca="false">G619/G620</f>
@@ -60732,7 +60732,7 @@
       </c>
       <c r="E622" s="15" t="n">
         <f aca="false">E621/D621-1</f>
-        <v>0.405143040900527</v>
+        <v>0.405143040900529</v>
       </c>
       <c r="F622" s="15" t="n">
         <f aca="false">F621/E621-1</f>
@@ -60740,7 +60740,7 @@
       </c>
       <c r="G622" s="15" t="n">
         <f aca="false">G621/F621-1</f>
-        <v>0.0795864507618838</v>
+        <v>0.0795864507618835</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60788,7 +60788,7 @@
       </c>
       <c r="D628" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E628" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60887,7 +60887,7 @@
       </c>
       <c r="D632" s="19" t="n">
         <f aca="false">D630*D631</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E632" s="19" t="n">
         <f aca="false">E630*E631</f>
@@ -60911,7 +60911,7 @@
       </c>
       <c r="D633" s="19" t="n">
         <f aca="false">D632*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E633" s="19" t="n">
         <f aca="false">E632*fx</f>
@@ -60986,7 +60986,7 @@
       </c>
       <c r="G636" s="15" t="n">
         <f aca="false">$D$634*G635</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61010,7 +61010,7 @@
       </c>
       <c r="G637" s="19" t="n">
         <f aca="false">G633*G636</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61061,11 +61061,11 @@
       </c>
       <c r="F639" s="19" t="n">
         <f aca="false">F637*(1-F638)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G639" s="19" t="n">
         <f aca="false">G637*(1-G638)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61122,7 +61122,7 @@
       </c>
       <c r="F642" s="19" t="n">
         <f aca="false">F639+F641</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G642" s="19" t="n">
         <f aca="false">G639+G641</f>
@@ -61142,11 +61142,11 @@
       </c>
       <c r="E643" s="15" t="n">
         <f aca="false">E642/D642-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F643" s="15" t="n">
         <f aca="false">F642/E642-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G643" s="15" t="n">
         <f aca="false">G642/F642-1</f>
@@ -61174,11 +61174,11 @@
       </c>
       <c r="F644" s="15" t="n">
         <f aca="false">F639/F642</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G644" s="15" t="n">
         <f aca="false">G639/G642</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61190,7 +61190,7 @@
       </c>
       <c r="D645" s="16" t="n">
         <f aca="false">D639/fx/D630</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E645" s="16" t="n">
         <f aca="false">E639/fx/E630</f>
@@ -61222,7 +61222,7 @@
       </c>
       <c r="F646" s="19" t="n">
         <f aca="false">F637/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G646" s="19" t="n">
         <f aca="false">G637/fx/odm_vr</f>
@@ -61273,7 +61273,7 @@
       </c>
       <c r="G649" s="21" t="n">
         <f aca="false">($D$648+d_ai+vrd_hi)*G637*(1-G638*(1-keep))</f>
-        <v>267.352380057938</v>
+        <v>267.352380057939</v>
       </c>
       <c r="H649" s="4" t="s">
         <v>423</v>
@@ -61379,7 +61379,7 @@
       </c>
       <c r="E653" s="19" t="n">
         <f aca="false">D653*(1+MAX(0,phi*E643))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F653" s="19" t="n">
         <f aca="false">E653*(1+MAX(0,phi*F643))</f>
@@ -61387,7 +61387,7 @@
       </c>
       <c r="G653" s="19" t="n">
         <f aca="false">F653*(1+MAX(0,phi*G643))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61407,7 +61407,7 @@
       </c>
       <c r="E654" s="19" t="n">
         <f aca="false">E653+0*E642</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F654" s="19" t="n">
         <f aca="false">F653+0*F642</f>
@@ -61415,7 +61415,7 @@
       </c>
       <c r="G654" s="19" t="n">
         <f aca="false">G653+0*G642</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61435,15 +61435,15 @@
       </c>
       <c r="E655" s="19" t="n">
         <f aca="false">E650-E654</f>
-        <v>208.838743649194</v>
+        <v>208.838743649195</v>
       </c>
       <c r="F655" s="19" t="n">
         <f aca="false">F650-F654</f>
-        <v>248.664933994852</v>
+        <v>248.664933994853</v>
       </c>
       <c r="G655" s="19" t="n">
         <f aca="false">G650-G654</f>
-        <v>268.251734802877</v>
+        <v>268.251734802878</v>
       </c>
     </row>
     <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61579,11 +61579,11 @@
       </c>
       <c r="F660" s="21" t="n">
         <f aca="false">F658/F659</f>
-        <v>55.8021773880161</v>
+        <v>55.8021773880162</v>
       </c>
       <c r="G660" s="21" t="n">
         <f aca="false">G658/G659</f>
-        <v>60.1975946090698</v>
+        <v>60.1975946090699</v>
       </c>
     </row>
     <row r="661" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61599,7 +61599,7 @@
       </c>
       <c r="E661" s="15" t="n">
         <f aca="false">E660/D660-1</f>
-        <v>0.631645944038603</v>
+        <v>0.631645944038605</v>
       </c>
       <c r="F661" s="15" t="n">
         <f aca="false">F660/E660-1</f>
@@ -61607,7 +61607,7 @@
       </c>
       <c r="G661" s="15" t="n">
         <f aca="false">G660/F660-1</f>
-        <v>0.0787678443170867</v>
+        <v>0.0787678443170861</v>
       </c>
     </row>
     <row r="664" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61655,7 +61655,7 @@
       </c>
       <c r="D667" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E667" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61754,7 +61754,7 @@
       </c>
       <c r="D671" s="19" t="n">
         <f aca="false">D669*D670</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E671" s="19" t="n">
         <f aca="false">E669*E670</f>
@@ -61778,7 +61778,7 @@
       </c>
       <c r="D672" s="19" t="n">
         <f aca="false">D671*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E672" s="19" t="n">
         <f aca="false">E671*fx</f>
@@ -61853,7 +61853,7 @@
       </c>
       <c r="G675" s="15" t="n">
         <f aca="false">$D$673*G674</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61877,7 +61877,7 @@
       </c>
       <c r="G676" s="19" t="n">
         <f aca="false">G672*G675</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61928,11 +61928,11 @@
       </c>
       <c r="F678" s="19" t="n">
         <f aca="false">F676*(1-F677)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G678" s="19" t="n">
         <f aca="false">G676*(1-G677)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61989,7 +61989,7 @@
       </c>
       <c r="F681" s="19" t="n">
         <f aca="false">F678+F680</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G681" s="19" t="n">
         <f aca="false">G678+G680</f>
@@ -62009,11 +62009,11 @@
       </c>
       <c r="E682" s="15" t="n">
         <f aca="false">E681/D681-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F682" s="15" t="n">
         <f aca="false">F681/E681-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G682" s="15" t="n">
         <f aca="false">G681/F681-1</f>
@@ -62041,11 +62041,11 @@
       </c>
       <c r="F683" s="15" t="n">
         <f aca="false">F678/F681</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G683" s="15" t="n">
         <f aca="false">G678/G681</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62057,7 +62057,7 @@
       </c>
       <c r="D684" s="16" t="n">
         <f aca="false">D678/fx/D669</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E684" s="16" t="n">
         <f aca="false">E678/fx/E669</f>
@@ -62089,7 +62089,7 @@
       </c>
       <c r="F685" s="19" t="n">
         <f aca="false">F676/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G685" s="19" t="n">
         <f aca="false">G676/fx/odm_vr</f>
@@ -62132,7 +62132,7 @@
       </c>
       <c r="E688" s="21" t="n">
         <f aca="false">($D$687+d_ai+vrd)*E676*(1-E677*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F688" s="21" t="n">
         <f aca="false">($D$687+d_ai+vrd)*F676*(1-F677*(1-keep))</f>
@@ -62140,7 +62140,7 @@
       </c>
       <c r="G688" s="21" t="n">
         <f aca="false">($D$687+d_ai+vrd)*G676*(1-G677*(1-keep))</f>
-        <v>248.799436346374</v>
+        <v>248.799436346375</v>
       </c>
       <c r="H688" s="4" t="s">
         <v>423</v>
@@ -62163,7 +62163,7 @@
       </c>
       <c r="E689" s="19" t="n">
         <f aca="false">$D$687*E680+E688</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F689" s="19" t="n">
         <f aca="false">$D$687*F680+F688</f>
@@ -62246,7 +62246,7 @@
       </c>
       <c r="E692" s="19" t="n">
         <f aca="false">D692*(1+MAX(0,phi*E682))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F692" s="19" t="n">
         <f aca="false">E692*(1+MAX(0,phi*F682))</f>
@@ -62254,7 +62254,7 @@
       </c>
       <c r="G692" s="19" t="n">
         <f aca="false">F692*(1+MAX(0,phi*G682))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62274,15 +62274,15 @@
       </c>
       <c r="E693" s="19" t="n">
         <f aca="false">E692+opx_adj_hi*E681</f>
-        <v>94.8004602988184</v>
+        <v>94.8004602988185</v>
       </c>
       <c r="F693" s="19" t="n">
         <f aca="false">F692+opx_adj_hi*F681</f>
-        <v>97.4327566905685</v>
+        <v>97.4327566905686</v>
       </c>
       <c r="G693" s="19" t="n">
         <f aca="false">G692+opx_adj_hi*G681</f>
-        <v>98.0608220999293</v>
+        <v>98.0608220999294</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62306,7 +62306,7 @@
       </c>
       <c r="F694" s="19" t="n">
         <f aca="false">F689-F693</f>
-        <v>219.292939619074</v>
+        <v>219.292939619075</v>
       </c>
       <c r="G694" s="19" t="n">
         <f aca="false">G689-G693</f>
@@ -62390,11 +62390,11 @@
       </c>
       <c r="F697" s="19" t="n">
         <f aca="false">F694*F696</f>
-        <v>189.688392770499</v>
+        <v>189.6883927705</v>
       </c>
       <c r="G697" s="19" t="n">
         <f aca="false">G694*G696</f>
-        <v>205.387343456396</v>
+        <v>205.387343456397</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62446,7 +62446,7 @@
       </c>
       <c r="F699" s="21" t="n">
         <f aca="false">F697/F698</f>
-        <v>49.2108932287832</v>
+        <v>49.2108932287833</v>
       </c>
       <c r="G699" s="21" t="n">
         <f aca="false">G697/G698</f>
@@ -62466,7 +62466,7 @@
       </c>
       <c r="E700" s="15" t="n">
         <f aca="false">E699/D699-1</f>
-        <v>0.429162689730097</v>
+        <v>0.429162689730098</v>
       </c>
       <c r="F700" s="15" t="n">
         <f aca="false">F699/E699-1</f>
@@ -62474,7 +62474,7 @@
       </c>
       <c r="G700" s="15" t="n">
         <f aca="false">G699/F699-1</f>
-        <v>0.0827617887241574</v>
+        <v>0.0827617887241572</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62522,7 +62522,7 @@
       </c>
       <c r="D706" s="21" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E706" s="21" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62621,7 +62621,7 @@
       </c>
       <c r="D710" s="19" t="n">
         <f aca="false">D708*D709</f>
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="E710" s="19" t="n">
         <f aca="false">E708*E709</f>
@@ -62645,7 +62645,7 @@
       </c>
       <c r="D711" s="19" t="n">
         <f aca="false">D710*fx</f>
-        <v>20307.7290011204</v>
+        <v>20307.7290011203</v>
       </c>
       <c r="E711" s="19" t="n">
         <f aca="false">E710*fx</f>
@@ -62720,7 +62720,7 @@
       </c>
       <c r="G714" s="15" t="n">
         <f aca="false">$D$712*G713</f>
-        <v>0.120506511578177</v>
+        <v>0.120506511578178</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62744,7 +62744,7 @@
       </c>
       <c r="G715" s="19" t="n">
         <f aca="false">G711*G714</f>
-        <v>6342.88673899625</v>
+        <v>6342.88673899626</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62795,11 +62795,11 @@
       </c>
       <c r="F717" s="19" t="n">
         <f aca="false">F715*(1-F716)</f>
-        <v>4701.90702893704</v>
+        <v>4701.90702893705</v>
       </c>
       <c r="G717" s="19" t="n">
         <f aca="false">G715*(1-G716)</f>
-        <v>4757.16505424718</v>
+        <v>4757.16505424719</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62856,7 +62856,7 @@
       </c>
       <c r="F720" s="19" t="n">
         <f aca="false">F717+F719</f>
-        <v>6046.24302221704</v>
+        <v>6046.24302221705</v>
       </c>
       <c r="G720" s="19" t="n">
         <f aca="false">G717+G719</f>
@@ -62876,11 +62876,11 @@
       </c>
       <c r="E721" s="15" t="n">
         <f aca="false">E720/D720-1</f>
-        <v>0.428086013528418</v>
+        <v>0.428086013528419</v>
       </c>
       <c r="F721" s="15" t="n">
         <f aca="false">F720/E720-1</f>
-        <v>0.0587923179477703</v>
+        <v>0.0587923179477705</v>
       </c>
       <c r="G721" s="15" t="n">
         <f aca="false">G720/F720-1</f>
@@ -62908,11 +62908,11 @@
       </c>
       <c r="F722" s="15" t="n">
         <f aca="false">F717/F720</f>
-        <v>0.777657631633361</v>
+        <v>0.777657631633362</v>
       </c>
       <c r="G722" s="15" t="n">
         <f aca="false">G717/G720</f>
-        <v>0.776250660827723</v>
+        <v>0.776250660827724</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62924,7 +62924,7 @@
       </c>
       <c r="D723" s="16" t="n">
         <f aca="false">D717/fx/D708</f>
-        <v>3.63138338873399</v>
+        <v>3.631383388734</v>
       </c>
       <c r="E723" s="16" t="n">
         <f aca="false">E717/fx/E708</f>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="F724" s="19" t="n">
         <f aca="false">F715/fx/odm_vr</f>
-        <v>27.2101101211634</v>
+        <v>27.2101101211635</v>
       </c>
       <c r="G724" s="19" t="n">
         <f aca="false">G715/fx/odm_vr</f>
@@ -62999,7 +62999,7 @@
       </c>
       <c r="E727" s="21" t="n">
         <f aca="false">($D$726+d_ai+vrd)*E715*(1-E716*(1-keep))</f>
-        <v>194.386226205805</v>
+        <v>194.386226205806</v>
       </c>
       <c r="F727" s="21" t="n">
         <f aca="false">($D$726+d_ai+vrd)*F715*(1-F716*(1-keep))</f>
@@ -63007,7 +63007,7 @@
       </c>
       <c r="G727" s="21" t="n">
         <f aca="false">($D$726+d_ai+vrd)*G715*(1-G716*(1-keep))</f>
-        <v>248.799436346374</v>
+        <v>248.799436346375</v>
       </c>
       <c r="H727" s="4" t="s">
         <v>423</v>
@@ -63030,7 +63030,7 @@
       </c>
       <c r="E728" s="19" t="n">
         <f aca="false">$D$726*E719+E727</f>
-        <v>277.722828772205</v>
+        <v>277.722828772206</v>
       </c>
       <c r="F728" s="19" t="n">
         <f aca="false">$D$726*F719+F727</f>
@@ -63113,7 +63113,7 @@
       </c>
       <c r="E731" s="19" t="n">
         <f aca="false">D731*(1+MAX(0,phi*E721))</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F731" s="19" t="n">
         <f aca="false">E731*(1+MAX(0,phi*F721))</f>
@@ -63121,7 +63121,7 @@
       </c>
       <c r="G731" s="19" t="n">
         <f aca="false">F731*(1+MAX(0,phi*G721))</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63141,7 +63141,7 @@
       </c>
       <c r="E732" s="19" t="n">
         <f aca="false">E731+0*E720</f>
-        <v>83.3794423716458</v>
+        <v>83.3794423716459</v>
       </c>
       <c r="F732" s="19" t="n">
         <f aca="false">F731+0*F720</f>
@@ -63149,7 +63149,7 @@
       </c>
       <c r="G732" s="19" t="n">
         <f aca="false">G731+0*G720</f>
-        <v>85.8040465651437</v>
+        <v>85.8040465651438</v>
       </c>
     </row>
     <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63177,7 +63177,7 @@
       </c>
       <c r="G733" s="19" t="n">
         <f aca="false">G728-G732</f>
-        <v>249.698791091313</v>
+        <v>249.698791091314</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63257,7 +63257,7 @@
       </c>
       <c r="F736" s="19" t="n">
         <f aca="false">F733*F735</f>
-        <v>173.539069247631</v>
+        <v>173.539069247632</v>
       </c>
       <c r="G736" s="19" t="n">
         <f aca="false">G733*G735</f>
@@ -63317,7 +63317,7 @@
       </c>
       <c r="G738" s="21" t="n">
         <f aca="false">G736/G737</f>
-        <v>48.5845510956663</v>
+        <v>48.5845510956664</v>
       </c>
     </row>
     <row r="739" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63333,7 +63333,7 @@
       </c>
       <c r="E739" s="15" t="n">
         <f aca="false">E738/D738-1</f>
-        <v>0.316527016592109</v>
+        <v>0.31652701659211</v>
       </c>
       <c r="F739" s="15" t="n">
         <f aca="false">F738/E738-1</f>
@@ -63341,7 +63341,7 @@
       </c>
       <c r="G739" s="15" t="n">
         <f aca="false">G738/F738-1</f>
-        <v>0.0791465814032595</v>
+        <v>0.0791465814032588</v>
       </c>
     </row>
     <row r="742" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63386,7 +63386,7 @@
       </c>
       <c r="E744" s="27" t="n">
         <f aca="false">tp_w_dcf*C744+(1-tp_w_dcf)*D744</f>
-        <v>566.562292345012</v>
+        <v>566.562292345013</v>
       </c>
       <c r="F744" s="15" t="n">
         <f aca="false">E744/E$744-1</f>
@@ -63402,7 +63402,7 @@
       </c>
       <c r="C745" s="27" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>558.131155474736</v>
+        <v>558.131155474737</v>
       </c>
       <c r="D745" s="27" t="n">
         <f aca="false">Val!B116</f>
@@ -63410,11 +63410,11 @@
       </c>
       <c r="E745" s="27" t="n">
         <f aca="false">tp_w_dcf*C745+(1-tp_w_dcf)*D745</f>
-        <v>523.49656338822</v>
+        <v>523.496563388221</v>
       </c>
       <c r="F745" s="15" t="n">
         <f aca="false">E745/E$744-1</f>
-        <v>-0.0760123459302989</v>
+        <v>-0.0760123459302987</v>
       </c>
     </row>
     <row r="746" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63426,7 +63426,7 @@
       </c>
       <c r="C746" s="27" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D89*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D90*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D91*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D92*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D93*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D94*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D94*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>764.806855288277</v>
+        <v>764.806855288278</v>
       </c>
       <c r="D746" s="27" t="n">
         <f aca="false">Val!B116</f>
@@ -63434,7 +63434,7 @@
       </c>
       <c r="E746" s="27" t="n">
         <f aca="false">tp_w_dcf*C746+(1-tp_w_dcf)*D746</f>
-        <v>626.83441329499</v>
+        <v>626.834413294991</v>
       </c>
       <c r="F746" s="15" t="n">
         <f aca="false">E746/E$744-1</f>
@@ -63450,7 +63450,7 @@
       </c>
       <c r="C747" s="27" t="n">
         <f aca="false">(tp_wA*(Val!B89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D89*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D90*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D91*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D92*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D93*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D94*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D94*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>708.513468912034</v>
+        <v>708.513468912035</v>
       </c>
       <c r="D747" s="27" t="n">
         <f aca="false">Val!B116</f>
@@ -63462,7 +63462,7 @@
       </c>
       <c r="F747" s="15" t="n">
         <f aca="false">E747/E$744-1</f>
-        <v>0.0567023753538007</v>
+        <v>0.056702375353801</v>
       </c>
     </row>
     <row r="748" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63486,7 +63486,7 @@
       </c>
       <c r="F748" s="15" t="n">
         <f aca="false">E748/E$744-1</f>
-        <v>-0.0387255104796274</v>
+        <v>-0.0387255104796271</v>
       </c>
     </row>
     <row r="749" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63506,7 +63506,7 @@
       </c>
       <c r="E749" s="27" t="n">
         <f aca="false">0.4*C749+(1-0.4)*D749</f>
-        <v>551.02222813635</v>
+        <v>551.022228136351</v>
       </c>
       <c r="F749" s="15" t="n">
         <f aca="false">E749/E$744-1</f>
@@ -63530,7 +63530,7 @@
       </c>
       <c r="E750" s="27" t="n">
         <f aca="false">0.8*C750+(1-0.8)*D750</f>
-        <v>613.182484970997</v>
+        <v>613.182484970998</v>
       </c>
       <c r="F750" s="15" t="n">
         <f aca="false">E750/E$744-1</f>

--- a/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
+++ b/quanta/dist/20261025_廣達模型_v0.2.1.xlsx
@@ -7341,26 +7341,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7578,26 +7578,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7699,26 +7699,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7820,26 +7820,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7941,26 +7941,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8062,26 +8062,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
